--- a/2026/GALERIA MITRE/Mayo/Mayo MITRE.xlsx
+++ b/2026/GALERIA MITRE/Mayo/Mayo MITRE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED90CDD-CF59-4813-9668-17D0F2FB94D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C3206A-73D7-4EC0-B86E-6B23BF1734A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$75</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$116</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="200">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -247,9 +252,6 @@
     <t>Banco  - Gastos bancarios</t>
   </si>
   <si>
-    <t>Transf 06/04</t>
-  </si>
-  <si>
     <t xml:space="preserve">Punitorios mal cobrados </t>
   </si>
   <si>
@@ -412,18 +414,6 @@
     <t>TELEFONO : 11-5320-2676 - MAIL: mitre686rc@gmail.com - OFICINA CON CITA PREVIA - DR MELO 2958 8° PISO</t>
   </si>
   <si>
-    <t>Debito 01/04</t>
-  </si>
-  <si>
-    <t>Hiedro Rodolfo Jorge - SAC vacaciones no gozadas - Indemnizacion por fallecimiento</t>
-  </si>
-  <si>
-    <t>Transf 08/04</t>
-  </si>
-  <si>
-    <t>Debito 10/04</t>
-  </si>
-  <si>
     <t xml:space="preserve">EDESUR - Cliente 000115764200 </t>
   </si>
   <si>
@@ -433,30 +423,15 @@
     <t>Metrogas - Cliente 030003582146</t>
   </si>
   <si>
-    <t>Debito 13/04</t>
-  </si>
-  <si>
     <t>Debito 16/04</t>
   </si>
   <si>
-    <t>Cuota 32/36 - planes de pago - Afip - contrib. de seg. social 06/2022 y 11/2022</t>
-  </si>
-  <si>
     <t xml:space="preserve">Planes de pago - Afip - aportes de seg. social 06/2022 y 11/2022 </t>
   </si>
   <si>
     <t xml:space="preserve">Seguro integral del consorcio-Federacion Patronal poliza 2215767 </t>
   </si>
   <si>
-    <t>Debito 27/04</t>
-  </si>
-  <si>
-    <t>Carrafiele Julio -  Transferencia realizada por adm. Saliente - Mes de Marzo</t>
-  </si>
-  <si>
-    <t>Ivana del Carmen Roldan -  Transferencia realizada por adm. Saliente - Mes de Marzo</t>
-  </si>
-  <si>
     <t>TOBIO DANIEL S.</t>
   </si>
   <si>
@@ -499,15 +474,9 @@
     <t>CARRARO JORGE</t>
   </si>
   <si>
-    <t>Deposito 07/04</t>
-  </si>
-  <si>
     <t>Nelida Micaela Atanes</t>
   </si>
   <si>
-    <t>Transf 14/04 - Rocio Aylin Aristiza</t>
-  </si>
-  <si>
     <t>Laura Boras</t>
   </si>
   <si>
@@ -517,36 +486,21 @@
     <t>Importante para dueños o inquilinos: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, dos locales), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</t>
   </si>
   <si>
-    <t>Deposito - 20/04</t>
-  </si>
-  <si>
     <t>Smurro Viviana - Jorge alberto Viera</t>
   </si>
   <si>
     <t>Colegio de farmaceuticos</t>
   </si>
   <si>
-    <t>Nelida micaela Atane - 22/04</t>
-  </si>
-  <si>
-    <t>Deposito 28/04</t>
-  </si>
-  <si>
     <t>Banco Galicia: Nro. De cuenta: 0000220-4716-6 - CBU: 0070716120000000220468 - Consorcio de propietarios Av. General Mite 686/92 - CUIT: 30-53618993-5</t>
   </si>
   <si>
-    <t>Honorarios administracion RC - Se adeudan</t>
-  </si>
-  <si>
     <t>Escribania Rodriguez - Aljandra Rodriguez</t>
   </si>
   <si>
     <t>Lucrecia Ines Carbone</t>
   </si>
   <si>
-    <t>Dinero Fondo FIMA - Al 07/05/2026</t>
-  </si>
-  <si>
     <t>Anotacion:</t>
   </si>
   <si>
@@ -566,9 +520,6 @@
   </si>
   <si>
     <t>Transf 22/05</t>
-  </si>
-  <si>
-    <t>Mozart SRL - Recarga de matafuegos</t>
   </si>
   <si>
     <t>Transf 18/05</t>
@@ -625,6 +576,63 @@
     <t>4401 y 4402 - Transfirio $91.683 y $4.000 el 13/05:   Adjunto este detalle:  Sicuso Fernando   4 401      $74738.46
 Sicuso Fernando    4 402      $ 20944.53
 Total :$95.682.99</t>
+  </si>
+  <si>
+    <t>TSG - Municipalidad de avellaneda</t>
+  </si>
+  <si>
+    <t>Reemplazo Sra. Isabel - Reemplazo de la Sra. Ivana</t>
+  </si>
+  <si>
+    <t>Cuota 33/36 - planes de pago - Afip - contrib. de seg. social 06/2022 y 11/2022</t>
+  </si>
+  <si>
+    <t>Mozart SRL - Recarga de matafuegos vencidos en diciembre</t>
+  </si>
+  <si>
+    <t>Debito 22/05</t>
+  </si>
+  <si>
+    <t>AySa</t>
+  </si>
+  <si>
+    <t>Transf 26/05</t>
+  </si>
+  <si>
+    <t>Gustavo Padron - Sr. Contador</t>
+  </si>
+  <si>
+    <t>No se debitaron</t>
+  </si>
+  <si>
+    <t>Honorarios administracion RC - Se adeudan 2 meses</t>
+  </si>
+  <si>
+    <t>Arreglo Reja - Sr Herrero Alan - Arreglo barrotes reja principal</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>Carrafiele Julio -  Mes de Abril</t>
+  </si>
+  <si>
+    <t>Ivana del Carmen Roldan -  Mes de Abril</t>
+  </si>
+  <si>
+    <t>Deposito ya identificado mes anterior</t>
+  </si>
+  <si>
+    <t>Juana Acuña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deposito 22/05 </t>
+  </si>
+  <si>
+    <t>Frisco</t>
+  </si>
+  <si>
+    <t>Dinero Fondo FIMA - Al 03/06/2026</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1287,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1464,9 +1472,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1491,7 +1496,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
@@ -1499,7 +1503,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1508,201 +1511,168 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1771,9 +1741,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1811,9 +1781,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1846,9 +1816,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1881,9 +1868,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2057,21 +2061,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L120"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L116"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.44140625" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="102" t="s">
         <v>64</v>
       </c>
@@ -2079,15 +2083,15 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="98" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" s="98"/>
       <c r="C2" s="98"/>
       <c r="D2" s="98"/>
     </row>
-    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="98" t="s">
         <v>71</v>
       </c>
@@ -2095,76 +2099,76 @@
       <c r="C3" s="98"/>
       <c r="D3" s="98"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="182" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="182"/>
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="186" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="186"/>
       <c r="C4" s="99"/>
       <c r="D4" s="99"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="182"/>
-      <c r="B5" s="182"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="186"/>
+      <c r="B5" s="186"/>
       <c r="C5" s="99"/>
       <c r="D5" s="99"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="182"/>
-      <c r="B6" s="182"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="186"/>
+      <c r="B6" s="186"/>
       <c r="C6" s="99"/>
       <c r="D6" s="99"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="182"/>
-      <c r="B7" s="182"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="186"/>
+      <c r="B7" s="186"/>
       <c r="C7" s="99"/>
       <c r="D7" s="99"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="195" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="195"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="195"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="182" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="182"/>
-      <c r="C14" s="182"/>
-      <c r="D14" s="182"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="182"/>
-      <c r="B15" s="182"/>
-      <c r="C15" s="182"/>
-      <c r="D15" s="182"/>
-    </row>
-    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="182"/>
-      <c r="B16" s="182"/>
-      <c r="C16" s="182"/>
-      <c r="D16" s="182"/>
-    </row>
-    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="182"/>
-      <c r="B17" s="182"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="181" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="181"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="181"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="186" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="186"/>
+      <c r="C14" s="186"/>
+      <c r="D14" s="186"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="186"/>
+      <c r="B15" s="186"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="186"/>
+    </row>
+    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="186"/>
+      <c r="B16" s="186"/>
+      <c r="C16" s="186"/>
+      <c r="D16" s="186"/>
+    </row>
+    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="186"/>
+      <c r="B17" s="186"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="186"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>26</v>
       </c>
@@ -2172,7 +2176,7 @@
       <c r="C21" s="8"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>52</v>
       </c>
@@ -2180,876 +2184,864 @@
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
     </row>
-    <row r="23" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="192" t="s">
-        <v>141</v>
-      </c>
-      <c r="B23" s="193"/>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="179" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="180"/>
       <c r="C23" s="113">
-        <v>560501.56999999995</v>
-      </c>
-      <c r="D23" s="69" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>939981.1</v>
+      </c>
+      <c r="D23" s="69"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>55</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="113"/>
+      <c r="C24" s="113">
+        <v>-148047.01999999999</v>
+      </c>
       <c r="D24" s="69"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="113"/>
+      <c r="C25" s="113">
+        <v>0.92</v>
+      </c>
       <c r="D25" s="69"/>
       <c r="G25" s="125"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="113"/>
-      <c r="D26" s="69"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="43" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="95">
-        <f>SUM(C23:C26)</f>
-        <v>560501.56999999995</v>
-      </c>
-      <c r="D27" s="43"/>
-    </row>
-    <row r="28" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="192" t="s">
-        <v>142</v>
-      </c>
-      <c r="B28" s="193"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="95">
+        <f>SUM(C23:C25)</f>
+        <v>791935</v>
+      </c>
+      <c r="D26" s="43"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="179" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="180"/>
+      <c r="C27" s="113">
+        <v>849606.52</v>
+      </c>
+      <c r="D27" s="69"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="5"/>
       <c r="C28" s="113">
-        <v>582828.23</v>
-      </c>
-      <c r="D28" s="69" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
+        <v>-210277.64</v>
+      </c>
+      <c r="D28" s="101"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="B29" s="5"/>
       <c r="C29" s="113">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="D29" s="101"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="113">
-        <v>0</v>
-      </c>
-      <c r="D30" s="101"/>
-    </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="100"/>
+      <c r="C30" s="44">
+        <f>SUM(C27:C29)</f>
+        <v>639329</v>
+      </c>
+      <c r="D30" s="70"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>182</v>
+      </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="128"/>
+      <c r="C31" s="128">
+        <f>250000+140000</f>
+        <v>390000</v>
+      </c>
       <c r="D31" s="101"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="43" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="128"/>
+      <c r="D32" s="101"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="100"/>
-      <c r="C32" s="44">
-        <f>SUM(C28:C31)</f>
-        <v>582828.23</v>
-      </c>
-      <c r="D32" s="70"/>
-    </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="190" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="191"/>
-      <c r="C33" s="113">
-        <v>1688447.15</v>
-      </c>
-      <c r="D33" s="101" t="s">
+      <c r="B33" s="100"/>
+      <c r="C33" s="44">
+        <f>SUM(C31:C32)</f>
+        <v>390000</v>
+      </c>
+      <c r="D33" s="70"/>
+    </row>
+    <row r="34" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="71">
+        <f>+C26+C33+C30</f>
+        <v>1821264</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="72"/>
+      <c r="F35" s="13"/>
+    </row>
+    <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="103" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" s="96"/>
+      <c r="C36" s="113"/>
+      <c r="D36" s="111"/>
+      <c r="G36" s="13"/>
+    </row>
+    <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="103" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37" s="96"/>
+      <c r="C37" s="113">
+        <v>135000</v>
+      </c>
+      <c r="D37" s="111" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="103" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="96"/>
+      <c r="C38" s="113">
+        <v>200000</v>
+      </c>
+      <c r="D38" s="111" t="s">
+        <v>168</v>
+      </c>
+      <c r="G38" s="13"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="17"/>
+      <c r="C39" s="164"/>
+      <c r="D39" s="71">
+        <f>SUM(C36:C38)</f>
+        <v>335000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="24"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="49"/>
+    </row>
+    <row r="41" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="183"/>
+      <c r="C41" s="127">
+        <v>111379</v>
+      </c>
+      <c r="D41" s="126" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="73">
+        <f>SUM(C41:C41)</f>
+        <v>111379</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="115"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="74"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="69"/>
+      <c r="C44" s="131">
+        <v>0</v>
+      </c>
+      <c r="D44" s="107"/>
+      <c r="F44" s="104"/>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="182" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45" s="183"/>
+      <c r="C45" s="131">
+        <v>11596.99</v>
+      </c>
+      <c r="D45" s="107" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="113">
-        <v>0</v>
-      </c>
-      <c r="D34" s="101"/>
-    </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="113">
-        <v>0</v>
-      </c>
-      <c r="D35" s="101"/>
-    </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="128"/>
-      <c r="D36" s="101"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="100"/>
-      <c r="C37" s="44">
-        <f>SUM(C33:C36)</f>
-        <v>1688447.15</v>
-      </c>
-      <c r="D37" s="70"/>
-      <c r="F37" s="13"/>
-    </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="71">
-        <f>+C27+C32+C37</f>
-        <v>2831776.9499999997</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="72"/>
-      <c r="F39" s="13"/>
-    </row>
-    <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="103" t="s">
-        <v>169</v>
-      </c>
-      <c r="B40" s="96"/>
-      <c r="C40" s="113"/>
-      <c r="D40" s="111"/>
-      <c r="G40" s="13"/>
-    </row>
-    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="103" t="s">
-        <v>185</v>
-      </c>
-      <c r="B41" s="96"/>
-      <c r="C41" s="170">
-        <v>200000</v>
-      </c>
-      <c r="D41" s="111" t="s">
-        <v>186</v>
-      </c>
-      <c r="G41" s="13"/>
-    </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="169"/>
-      <c r="D42" s="71">
-        <f>SUM(C40:C41)</f>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="24"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="49"/>
-    </row>
-    <row r="44" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="186" t="s">
-        <v>139</v>
-      </c>
-      <c r="B44" s="187"/>
-      <c r="C44" s="127">
-        <v>111379</v>
-      </c>
-      <c r="D44" s="126" t="s">
+      <c r="F45" s="104"/>
+    </row>
+    <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="182" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" s="183"/>
+      <c r="C46" s="131">
+        <v>11930.96</v>
+      </c>
+      <c r="D46" s="107" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" s="104"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="C47" s="116">
+        <v>0</v>
+      </c>
+      <c r="D47" s="110"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="C48" s="116">
+        <v>0</v>
+      </c>
+      <c r="D48" s="110">
+        <f>D47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B49" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="116">
+        <v>0</v>
+      </c>
+      <c r="D49" s="108">
+        <f>D47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="115"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="73">
+        <f>SUM(C44:C49)</f>
+        <v>23527.949999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="115"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="74"/>
+    </row>
+    <row r="52" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="69" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="186" t="s">
-        <v>139</v>
-      </c>
-      <c r="B45" s="187"/>
-      <c r="C45" s="127">
-        <v>111379</v>
-      </c>
-      <c r="D45" s="126" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="73">
-        <f>SUM(C44:C45)</f>
-        <v>222758</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="115"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="74"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="69"/>
-      <c r="C48" s="131">
-        <v>553656.43999999994</v>
-      </c>
-      <c r="D48" s="107" t="s">
-        <v>131</v>
-      </c>
-      <c r="F48" s="104"/>
-    </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="186" t="s">
-        <v>137</v>
-      </c>
-      <c r="B49" s="187"/>
-      <c r="C49" s="131">
-        <v>11596.99</v>
-      </c>
-      <c r="D49" s="107" t="s">
-        <v>136</v>
-      </c>
-      <c r="F49" s="104"/>
-    </row>
-    <row r="50" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="186" t="s">
-        <v>138</v>
-      </c>
-      <c r="B50" s="187"/>
-      <c r="C50" s="131">
-        <v>11596.99</v>
-      </c>
-      <c r="D50" s="107" t="s">
-        <v>136</v>
-      </c>
-      <c r="F50" s="104"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="B51" s="69"/>
-      <c r="C51" s="116">
-        <v>7110.08</v>
-      </c>
-      <c r="D51" s="110" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="69" t="s">
-        <v>67</v>
       </c>
       <c r="B52" s="69"/>
       <c r="C52" s="116">
-        <v>133842.97</v>
-      </c>
-      <c r="D52" s="110" t="str">
-        <f>D51</f>
-        <v>Debito 13/04</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="D52" s="107"/>
+    </row>
+    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="69" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="B53" s="69"/>
       <c r="C53" s="116">
-        <v>63990.68</v>
-      </c>
-      <c r="D53" s="108" t="str">
-        <f>D51</f>
-        <v>Debito 13/04</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="B54" s="115"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="73">
-        <f>SUM(C48:C53)</f>
-        <v>781794.14999999991</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="115"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="74"/>
-    </row>
-    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130169.33</v>
+      </c>
+      <c r="D53" s="107" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="B54" s="69"/>
+      <c r="C54" s="116">
+        <v>1322015.6299999999</v>
+      </c>
+      <c r="D54" s="107" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="69" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="69"/>
+      <c r="C55" s="116">
+        <v>35276.449999999997</v>
+      </c>
+      <c r="D55" s="107" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="69" t="s">
-        <v>133</v>
-      </c>
-      <c r="B56" s="69"/>
+        <v>181</v>
+      </c>
+      <c r="B56" s="132"/>
       <c r="C56" s="116">
-        <v>362714.81</v>
+        <v>78534</v>
       </c>
       <c r="D56" s="107" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="69" t="s">
-        <v>132</v>
-      </c>
-      <c r="B57" s="69"/>
-      <c r="C57" s="116">
-        <v>133269.18</v>
-      </c>
-      <c r="D57" s="107" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="69" t="s">
-        <v>134</v>
-      </c>
-      <c r="B58" s="69"/>
-      <c r="C58" s="116">
-        <v>34422.57</v>
-      </c>
-      <c r="D58" s="107" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="69"/>
-      <c r="B59" s="132"/>
-      <c r="C59" s="116"/>
-      <c r="D59" s="107"/>
-    </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="24" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B60" s="24"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="73">
-        <f>SUM(C56:C59)</f>
-        <v>530406.55999999994</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="23" t="s">
+      <c r="B57" s="24"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="73">
+        <f>SUM(C52:C56)</f>
+        <v>1565995.41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="76"/>
-    </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="188" t="s">
-        <v>182</v>
-      </c>
-      <c r="B62" s="189"/>
-      <c r="C62" s="168">
+      <c r="B58" s="24"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="76"/>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="184" t="s">
+        <v>164</v>
+      </c>
+      <c r="B59" s="185"/>
+      <c r="C59" s="116">
         <v>171600</v>
       </c>
-      <c r="D62" s="107" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="188" t="s">
+      <c r="D59" s="107" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="184" t="s">
+        <v>166</v>
+      </c>
+      <c r="B60" s="185"/>
+      <c r="C60" s="116">
+        <v>326000</v>
+      </c>
+      <c r="D60" s="107" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="184" t="s">
+        <v>191</v>
+      </c>
+      <c r="B61" s="185"/>
+      <c r="C61" s="116">
+        <v>90000</v>
+      </c>
+      <c r="D61" s="225" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="182" t="s">
+        <v>161</v>
+      </c>
+      <c r="B62" s="183"/>
+      <c r="C62" s="116">
+        <v>180000</v>
+      </c>
+      <c r="D62" s="109" t="s">
+        <v>162</v>
+      </c>
+      <c r="E62" s="116"/>
+      <c r="F62" s="37"/>
+    </row>
+    <row r="63" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="182" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="189"/>
-      <c r="C63" s="168">
-        <v>326000</v>
-      </c>
-      <c r="D63" s="107" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="186" t="s">
-        <v>178</v>
-      </c>
-      <c r="B64" s="187"/>
-      <c r="C64" s="168">
-        <v>180000</v>
+      <c r="B63" s="183"/>
+      <c r="C63" s="116">
+        <v>1745880</v>
+      </c>
+      <c r="D63" s="109" t="s">
+        <v>163</v>
+      </c>
+      <c r="E63" s="116"/>
+      <c r="F63" s="37"/>
+    </row>
+    <row r="64" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="184" t="s">
+        <v>170</v>
+      </c>
+      <c r="B64" s="185"/>
+      <c r="C64" s="116">
+        <v>77600</v>
       </c>
       <c r="D64" s="109" t="s">
-        <v>179</v>
-      </c>
-      <c r="E64" s="116"/>
+        <v>168</v>
+      </c>
+      <c r="E64" s="165"/>
       <c r="F64" s="37"/>
     </row>
-    <row r="65" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="186" t="s">
-        <v>180</v>
-      </c>
-      <c r="B65" s="187"/>
-      <c r="C65" s="168">
-        <v>1746879.95</v>
+    <row r="65" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="184" t="s">
+        <v>171</v>
+      </c>
+      <c r="B65" s="185"/>
+      <c r="C65" s="116">
+        <v>95700</v>
       </c>
       <c r="D65" s="109" t="s">
-        <v>181</v>
-      </c>
-      <c r="E65" s="116"/>
+        <v>168</v>
+      </c>
+      <c r="E65" s="165"/>
       <c r="F65" s="37"/>
     </row>
-    <row r="66" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="188" t="s">
-        <v>188</v>
-      </c>
-      <c r="B66" s="189"/>
-      <c r="C66" s="168">
-        <v>77600</v>
+    <row r="66" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="184" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66" s="185"/>
+      <c r="C66" s="116">
+        <v>46200</v>
       </c>
       <c r="D66" s="109" t="s">
-        <v>186</v>
-      </c>
-      <c r="E66" s="171"/>
+        <v>168</v>
+      </c>
+      <c r="E66" s="37"/>
       <c r="F66" s="37"/>
     </row>
-    <row r="67" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="188" t="s">
-        <v>189</v>
-      </c>
-      <c r="B67" s="189"/>
-      <c r="C67" s="168">
-        <v>95700</v>
-      </c>
-      <c r="D67" s="109" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="171"/>
-      <c r="F67" s="37"/>
-    </row>
-    <row r="68" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="188" t="s">
-        <v>187</v>
-      </c>
-      <c r="B68" s="189"/>
-      <c r="C68" s="168">
-        <v>46200</v>
-      </c>
-      <c r="D68" s="109" t="s">
-        <v>186</v>
-      </c>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-    </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="24" t="s">
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="79">
-        <f>SUM(C62:C68)</f>
-        <v>2643979.9500000002</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="23" t="s">
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="79">
+        <f>SUM(C59:C66)</f>
+        <v>2732980</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B70" s="117"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="76"/>
-    </row>
-    <row r="71" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="186" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" s="187"/>
-      <c r="C71" s="116">
+      <c r="B68" s="117"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="76"/>
+    </row>
+    <row r="69" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="182" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="183"/>
+      <c r="C69" s="116">
         <v>60000</v>
       </c>
-      <c r="D71" s="80"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="69" t="s">
+      <c r="D69" s="80"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="69"/>
-      <c r="C72" s="116">
-        <f>330+93098.23</f>
-        <v>93428.23</v>
-      </c>
-      <c r="D72" s="78"/>
-    </row>
-    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="42" t="s">
+      <c r="B70" s="69"/>
+      <c r="C70" s="116">
+        <f>129893.2</f>
+        <v>129893.2</v>
+      </c>
+      <c r="D70" s="78"/>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="B73" s="42"/>
-      <c r="C73" s="81"/>
-      <c r="D73" s="73">
-        <f>SUM(C71:C72)</f>
-        <v>153428.22999999998</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="69"/>
-      <c r="D74" s="82"/>
-    </row>
-    <row r="75" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="183" t="s">
+      <c r="B71" s="42"/>
+      <c r="C71" s="81"/>
+      <c r="D71" s="73">
+        <f>SUM(C69:C70)</f>
+        <v>189893.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="69"/>
+      <c r="D72" s="82"/>
+    </row>
+    <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="187" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="184"/>
-      <c r="C75" s="185"/>
-      <c r="D75" s="83"/>
-    </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="1"/>
+      <c r="B73" s="188"/>
+      <c r="C73" s="189"/>
+      <c r="D73" s="83"/>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1"/>
+      <c r="C74" s="84"/>
+      <c r="D74" s="85"/>
+      <c r="E74" s="37"/>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B75" s="9"/>
+      <c r="C75" s="86"/>
+      <c r="D75" s="87">
+        <f>(SUM(D23:D73))</f>
+        <v>6780039.5600000005</v>
+      </c>
+      <c r="E75" s="37"/>
+      <c r="F75" s="37"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C76" s="84"/>
-      <c r="D76" s="85"/>
-      <c r="E76" s="37"/>
-    </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" s="9"/>
-      <c r="C77" s="86"/>
-      <c r="D77" s="87">
-        <f>(SUM(D23:D75))</f>
-        <v>7364143.8399999999</v>
-      </c>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C78" s="84"/>
-      <c r="D78" s="84"/>
-      <c r="F78" s="105"/>
-    </row>
-    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C79" s="84"/>
-      <c r="D79" s="84"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="10" t="s">
+      <c r="D76" s="84"/>
+      <c r="F76" s="105"/>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="84"/>
+      <c r="D77" s="84"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B80" s="11"/>
-      <c r="C80" s="88"/>
-      <c r="D80" s="89"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="192"/>
-      <c r="B81" s="193"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="88"/>
+      <c r="D78" s="89"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="179"/>
+      <c r="B79" s="180"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="75"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="179"/>
+      <c r="B80" s="180"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="75"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="92"/>
+      <c r="B81" s="93"/>
       <c r="C81" s="77"/>
       <c r="D81" s="75"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="192"/>
-      <c r="B82" s="193"/>
-      <c r="C82" s="77"/>
-      <c r="D82" s="75"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="92"/>
-      <c r="B83" s="93"/>
-      <c r="C83" s="77"/>
-      <c r="D83" s="75"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="40"/>
-      <c r="B84" s="39"/>
-      <c r="C84" s="45"/>
-      <c r="D84" s="45">
-        <f>SUM(C81:C83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="19" t="s">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="40"/>
+      <c r="B82" s="39"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45">
+        <f>SUM(C79:C81)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B87" s="19"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
+      <c r="B85" s="19"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B89" s="9"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="50">
-        <f>D84+D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="9"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="50">
+        <f>D82+D85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" s="68">
+        <f>D75</f>
+        <v>6780039.5600000005</v>
+      </c>
+      <c r="C89" s="37"/>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" s="68">
+        <f>D75-D73</f>
+        <v>6780039.5600000005</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="67" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B91" s="68">
-        <f>D77</f>
-        <v>7364143.8399999999</v>
-      </c>
-      <c r="C91" s="37"/>
-    </row>
-    <row r="92" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>D87-D85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="67" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="B92" s="68">
-        <f>D77-D75</f>
-        <v>7364143.8399999999</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="B93" s="68">
-        <f>D89-D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B94" s="68">
-        <f>D89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="14" t="s">
+        <f>D87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B98" s="34"/>
-    </row>
-    <row r="99" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="22" t="s">
+      <c r="B96" s="34"/>
+    </row>
+    <row r="97" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B99" s="94">
-        <v>4038909.89</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15" t="s">
+      <c r="B97" s="94">
+        <v>2090238.5600000024</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B100" s="35">
+      <c r="B98" s="35">
         <f>PRORRATEO!G66</f>
-        <v>2804769.5600000005</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4171978.8499999996</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="B99" s="78">
+        <f>B115</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="133" t="s">
+        <v>195</v>
+      </c>
+      <c r="B100" s="106">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="133" t="s">
-        <v>61</v>
-      </c>
-      <c r="B101" s="78">
-        <f>B119</f>
-        <v>391723</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+      <c r="B101" s="106">
+        <v>-46400</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B102" s="106">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="33" t="s">
         <v>43</v>
       </c>
       <c r="B103" s="106">
-        <f>-B92</f>
-        <v>-7364143.8399999999</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+        <f>-B90</f>
+        <v>-6780039.5600000005</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
         <v>44</v>
       </c>
       <c r="B104" s="78">
-        <f>-(B93)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+        <f>-(B91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="21" t="s">
         <v>11</v>
       </c>
       <c r="B105" s="94">
-        <f>SUM(B99:B104)</f>
-        <v>-128741.38999999873</v>
+        <f>SUM(B97:B104)</f>
+        <v>-14222.14999999851</v>
       </c>
       <c r="D105" s="129"/>
     </row>
-    <row r="106" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2"/>
       <c r="B106" s="134"/>
       <c r="D106" s="129"/>
     </row>
-    <row r="107" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="147" t="s">
-        <v>172</v>
-      </c>
-      <c r="B107" s="148">
+    <row r="107" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="B107" s="147">
         <v>1331900.92</v>
       </c>
       <c r="D107" s="129"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="134"/>
       <c r="D108" s="129"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="134"/>
       <c r="D109" s="129"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="134"/>
       <c r="D110" s="129"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D111" s="130"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="194" t="s">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="B112" s="194"/>
-    </row>
-    <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="194"/>
-      <c r="B113" s="194"/>
-    </row>
-    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B112" s="178"/>
+    </row>
+    <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="178"/>
+      <c r="B113" s="178"/>
+    </row>
+    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="90" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="B114" s="28">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="90" t="s">
-        <v>163</v>
-      </c>
-      <c r="B115" s="28">
-        <v>64500</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="90" t="s">
-        <v>167</v>
-      </c>
-      <c r="B116" s="28">
-        <v>210000</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="90" t="s">
-        <v>166</v>
-      </c>
-      <c r="B117" s="28">
-        <v>46400</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="90" t="s">
-        <v>159</v>
-      </c>
-      <c r="B118" s="28">
-        <v>20823</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" s="38" t="s">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B119" s="91">
-        <f>SUM(B114:B118)</f>
-        <v>391723</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L120" s="7"/>
+      <c r="B115" s="91">
+        <f>SUM(B114:B114)</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L116" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A112:B113"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A67:B67"/>
+  <mergeCells count="21">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A73:C73"/>
     <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3060,32 +3052,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="196" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C1" s="197"/>
       <c r="D1" s="197"/>
@@ -3095,18 +3087,22 @@
       <c r="H1" s="197"/>
       <c r="I1" s="197"/>
       <c r="J1" s="198"/>
-      <c r="K1" s="143" t="s">
+      <c r="K1" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="140">
-        <v>5145163.8899999987</v>
-      </c>
-      <c r="O1" s="141"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
+      <c r="N1" s="139">
+        <f>Q1</f>
+        <v>6780039.5600000005</v>
+      </c>
+      <c r="O1" s="140"/>
       <c r="P1" s="13"/>
-    </row>
-    <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q1">
+        <v>6780039.5600000005</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="199"/>
       <c r="C2" s="200"/>
@@ -3117,73 +3113,73 @@
       <c r="H2" s="200"/>
       <c r="I2" s="200"/>
       <c r="J2" s="201"/>
-      <c r="K2" s="145" t="s">
+      <c r="K2" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
+      <c r="L2" s="145"/>
+      <c r="M2" s="145"/>
       <c r="N2" s="114">
         <v>0</v>
       </c>
-      <c r="O2" s="142"/>
-    </row>
-    <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O2" s="141"/>
+    </row>
+    <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="215" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="216"/>
-      <c r="D3" s="216"/>
-      <c r="E3" s="216"/>
-      <c r="F3" s="216"/>
-      <c r="G3" s="216"/>
-      <c r="H3" s="216"/>
-      <c r="I3" s="216"/>
-      <c r="J3" s="216"/>
-      <c r="K3" s="216"/>
-      <c r="L3" s="216"/>
-      <c r="M3" s="216"/>
-      <c r="N3" s="216"/>
-      <c r="O3" s="217"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="218" t="s">
+      <c r="B3" s="213" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
+      <c r="M3" s="214"/>
+      <c r="N3" s="214"/>
+      <c r="O3" s="215"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="190" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="220" t="s">
+      <c r="B4" s="192" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="194" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="194" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="205" t="s">
+      <c r="F4" s="194" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="205" t="s">
+      <c r="G4" s="194" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="205" t="s">
+      <c r="H4" s="194" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="210" t="s">
+      <c r="I4" s="208" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="206" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="207" t="s">
+      <c r="K4" s="206" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="206" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="213" t="s">
+      <c r="M4" s="211" t="s">
         <v>58</v>
       </c>
       <c r="N4" s="47" t="s">
@@ -3194,27 +3190,27 @@
       </c>
       <c r="R4" s="37"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="219"/>
-      <c r="B5" s="221"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="206"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="208"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="208"/>
-      <c r="M5" s="214"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="191"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="195"/>
+      <c r="G5" s="195"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="207"/>
+      <c r="K5" s="210"/>
+      <c r="L5" s="207"/>
+      <c r="M5" s="212"/>
       <c r="N5" s="46" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 18/06</v>
       </c>
       <c r="O5" s="203"/>
     </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3222,16 +3218,16 @@
         <v>0</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" s="51">
         <v>1.58</v>
       </c>
       <c r="F6" s="52">
-        <v>1314382</v>
+        <v>1434450</v>
       </c>
       <c r="G6" s="53">
         <v>0</v>
@@ -3239,11 +3235,11 @@
       <c r="H6" s="54"/>
       <c r="I6" s="55">
         <f>F6-G6</f>
-        <v>1314382</v>
+        <v>1434450</v>
       </c>
       <c r="J6" s="55">
         <f>IF(I6&gt;0,I6*2.95%,0)</f>
-        <v>38774.269</v>
+        <v>42316.275000000001</v>
       </c>
       <c r="K6" s="56">
         <f>N$2*E6%</f>
@@ -3251,39 +3247,39 @@
       </c>
       <c r="L6" s="56">
         <f>N$1*E6%</f>
-        <v>81293.589461999989</v>
+        <v>107124.62504800002</v>
       </c>
       <c r="M6" s="57">
         <v>0</v>
       </c>
       <c r="N6" s="58">
         <f t="shared" ref="N6:N64" si="0">ROUND(SUM(I6:M6),0) + P6</f>
-        <v>1434450</v>
+        <v>1583891</v>
       </c>
       <c r="O6" s="59">
         <f t="shared" ref="O6:O64" si="1">ROUND(N6*3%,0) + N6</f>
-        <v>1477484</v>
+        <v>1631408</v>
       </c>
       <c r="P6" s="37">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="48">
         <v>1</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" s="51">
         <v>2.91</v>
       </c>
       <c r="F7" s="52">
-        <v>104780.01</v>
+        <v>257595.01</v>
       </c>
       <c r="G7" s="53">
         <v>0</v>
@@ -3291,11 +3287,11 @@
       <c r="H7" s="54"/>
       <c r="I7" s="55">
         <f>F7-G7</f>
-        <v>104780.01</v>
+        <v>257595.01</v>
       </c>
       <c r="J7" s="55">
         <f>IF(I7&gt;0,I7*2.95%,0)</f>
-        <v>3091.010295</v>
+        <v>7599.0527950000005</v>
       </c>
       <c r="K7" s="56">
         <f>N$2*E7%</f>
@@ -3303,25 +3299,25 @@
       </c>
       <c r="L7" s="56">
         <f>N$1*E7%</f>
-        <v>149724.26919899997</v>
+        <v>197299.15119600002</v>
       </c>
       <c r="M7" s="57">
         <v>0</v>
       </c>
       <c r="N7" s="58">
         <f t="shared" si="0"/>
-        <v>257595.01</v>
+        <v>462493.01</v>
       </c>
       <c r="O7" s="59">
         <f t="shared" si="1"/>
-        <v>265323.01</v>
+        <v>476368.01</v>
       </c>
       <c r="P7" s="37">
         <f>P5+0.01</f>
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3330,28 +3326,26 @@
         <v>2</v>
       </c>
       <c r="C8" s="118" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" s="118" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" s="119">
         <v>1.94</v>
       </c>
       <c r="F8" s="53">
-        <v>1246720.02</v>
-      </c>
-      <c r="G8" s="53">
-        <v>273000</v>
-      </c>
+        <v>1102261.02</v>
+      </c>
+      <c r="G8" s="53"/>
       <c r="H8" s="54"/>
       <c r="I8" s="120">
         <f t="shared" ref="I8:I64" si="2">F8-G8</f>
-        <v>973720.02</v>
+        <v>1102261.02</v>
       </c>
       <c r="J8" s="120">
         <f t="shared" ref="J8:J64" si="3">IF(I8&gt;0,I8*2.95%,0)</f>
-        <v>28724.740590000001</v>
+        <v>32516.700090000002</v>
       </c>
       <c r="K8" s="121">
         <f t="shared" ref="K8:K64" si="4">N$2*E8%</f>
@@ -3359,18 +3353,18 @@
       </c>
       <c r="L8" s="121">
         <f t="shared" ref="L8:L64" si="5">N$1*E8%</f>
-        <v>99816.179465999972</v>
+        <v>131532.767464</v>
       </c>
       <c r="M8" s="122">
         <v>0</v>
       </c>
       <c r="N8" s="123">
         <f t="shared" si="0"/>
-        <v>1102261.02</v>
+        <v>1266310.02</v>
       </c>
       <c r="O8" s="124">
         <f t="shared" si="1"/>
-        <v>1135329.02</v>
+        <v>1304299.02</v>
       </c>
       <c r="P8" s="37">
         <f>P7+0.01</f>
@@ -3378,7 +3372,7 @@
       </c>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
@@ -3387,25 +3381,24 @@
         <v>3</v>
       </c>
       <c r="C9" s="118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" s="135" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" s="119">
         <v>1.78</v>
       </c>
       <c r="F9" s="53">
-        <v>63905.03</v>
+        <v>91584.03</v>
       </c>
       <c r="G9" s="53">
-        <f>F9</f>
-        <v>63905.03</v>
+        <v>94332.03</v>
       </c>
       <c r="H9" s="54"/>
       <c r="I9" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2748</v>
       </c>
       <c r="J9" s="120">
         <f t="shared" si="3"/>
@@ -3417,25 +3410,25 @@
       </c>
       <c r="L9" s="121">
         <f t="shared" si="5"/>
-        <v>91583.917241999981</v>
+        <v>120684.70416800001</v>
       </c>
       <c r="M9" s="122">
         <v>0</v>
       </c>
       <c r="N9" s="123">
         <f t="shared" si="0"/>
-        <v>91584.03</v>
+        <v>117937.03</v>
       </c>
       <c r="O9" s="124">
         <f t="shared" si="1"/>
-        <v>94332.03</v>
+        <v>121475.03</v>
       </c>
       <c r="P9" s="37">
         <f>P8+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3443,21 +3436,21 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="C10" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>80</v>
+      <c r="C10" s="118" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="118" t="s">
+        <v>79</v>
       </c>
       <c r="E10" s="51">
         <v>1.62</v>
       </c>
       <c r="F10" s="52">
-        <v>60220.04</v>
+        <v>85853.07</v>
       </c>
       <c r="G10" s="53">
         <f>F10</f>
-        <v>60220.04</v>
+        <v>85853.07</v>
       </c>
       <c r="H10" s="54"/>
       <c r="I10" s="55">
@@ -3474,29 +3467,29 @@
       </c>
       <c r="L10" s="56">
         <f t="shared" si="5"/>
-        <v>83351.65501799999</v>
+        <v>109836.64087200003</v>
       </c>
       <c r="M10" s="57">
         <v>0</v>
       </c>
       <c r="N10" s="58">
         <f t="shared" si="0"/>
-        <v>83352.039999999994</v>
+        <v>109837.04</v>
       </c>
       <c r="O10" s="59">
         <f t="shared" si="1"/>
-        <v>85853.04</v>
+        <v>113132.04</v>
       </c>
       <c r="P10" s="37">
         <f t="shared" ref="P10:P64" si="7">P9+0.01</f>
         <v>0.04</v>
       </c>
       <c r="Q10" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R10" s="37"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -3504,17 +3497,17 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="C11" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="D11" s="48" t="s">
-        <v>81</v>
+      <c r="C11" s="118" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="118" t="s">
+        <v>80</v>
       </c>
       <c r="E11" s="51">
         <v>1.94</v>
       </c>
       <c r="F11" s="52">
-        <v>652261.05000000005</v>
+        <v>771319.05</v>
       </c>
       <c r="G11" s="53">
         <v>0</v>
@@ -3522,11 +3515,11 @@
       <c r="H11" s="54"/>
       <c r="I11" s="55">
         <f t="shared" si="2"/>
-        <v>652261.05000000005</v>
+        <v>771319.05</v>
       </c>
       <c r="J11" s="55">
         <f t="shared" si="3"/>
-        <v>19241.700975000003</v>
+        <v>22753.911975000003</v>
       </c>
       <c r="K11" s="56">
         <f t="shared" si="4"/>
@@ -3534,18 +3527,18 @@
       </c>
       <c r="L11" s="56">
         <f t="shared" si="5"/>
-        <v>99816.179465999972</v>
+        <v>131532.767464</v>
       </c>
       <c r="M11" s="57">
         <v>0</v>
       </c>
       <c r="N11" s="58">
         <f t="shared" si="0"/>
-        <v>771319.05</v>
+        <v>925606.05</v>
       </c>
       <c r="O11" s="59">
         <f t="shared" si="1"/>
-        <v>794459.05</v>
+        <v>953374.05</v>
       </c>
       <c r="P11" s="37">
         <f t="shared" si="7"/>
@@ -3553,27 +3546,27 @@
       </c>
       <c r="R11" s="37"/>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="118">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="C12" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>82</v>
+      <c r="C12" s="118" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="118" t="s">
+        <v>81</v>
       </c>
       <c r="E12" s="51">
         <v>1.78</v>
       </c>
       <c r="F12" s="52">
-        <v>63905.06</v>
+        <v>94332.06</v>
       </c>
       <c r="G12" s="53">
         <f>F12</f>
-        <v>63905.06</v>
+        <v>94332.06</v>
       </c>
       <c r="H12" s="54"/>
       <c r="I12" s="55">
@@ -3590,18 +3583,18 @@
       </c>
       <c r="L12" s="56">
         <f t="shared" si="5"/>
-        <v>91583.917241999981</v>
+        <v>120684.70416800001</v>
       </c>
       <c r="M12" s="57">
         <v>0</v>
       </c>
       <c r="N12" s="58">
         <f t="shared" si="0"/>
-        <v>91584.06</v>
+        <v>120685.06</v>
       </c>
       <c r="O12" s="59">
         <f t="shared" si="1"/>
-        <v>94332.06</v>
+        <v>124306.06</v>
       </c>
       <c r="P12" s="37">
         <f t="shared" si="7"/>
@@ -3609,27 +3602,27 @@
       </c>
       <c r="R12" s="37"/>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="118">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="C13" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>83</v>
+      <c r="C13" s="118" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="118" t="s">
+        <v>82</v>
       </c>
       <c r="E13" s="51">
         <v>1.62</v>
       </c>
       <c r="F13" s="52">
-        <v>60220.07</v>
+        <v>85853.07</v>
       </c>
       <c r="G13" s="53">
         <f>F13</f>
-        <v>60220.07</v>
+        <v>85853.07</v>
       </c>
       <c r="H13" s="54"/>
       <c r="I13" s="55">
@@ -3646,53 +3639,53 @@
       </c>
       <c r="L13" s="56">
         <f t="shared" si="5"/>
-        <v>83351.65501799999</v>
+        <v>109836.64087200003</v>
       </c>
       <c r="M13" s="57">
         <v>0</v>
       </c>
       <c r="N13" s="58">
         <f t="shared" si="0"/>
-        <v>83352.070000000007</v>
+        <v>109837.07</v>
       </c>
       <c r="O13" s="59">
         <f t="shared" si="1"/>
-        <v>85853.07</v>
+        <v>113132.07</v>
       </c>
       <c r="P13" s="37">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q13" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R13" s="37"/>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="176">
+      <c r="B14" s="118">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="C14" s="176" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="176" t="s">
-        <v>84</v>
+      <c r="C14" s="118" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="118" t="s">
+        <v>83</v>
       </c>
       <c r="E14" s="51">
         <v>1.62</v>
       </c>
       <c r="F14" s="52">
-        <v>57704.08</v>
+        <v>83056.08</v>
       </c>
       <c r="G14" s="53">
-        <v>58000</v>
+        <v>83420</v>
       </c>
       <c r="H14" s="54"/>
       <c r="I14" s="55">
         <f t="shared" si="2"/>
-        <v>-295.91999999999825</v>
+        <v>-363.91999999999825</v>
       </c>
       <c r="J14" s="55">
         <f t="shared" si="3"/>
@@ -3704,18 +3697,18 @@
       </c>
       <c r="L14" s="56">
         <f t="shared" si="5"/>
-        <v>83351.65501799999</v>
+        <v>109836.64087200003</v>
       </c>
       <c r="M14" s="57">
         <v>0</v>
       </c>
       <c r="N14" s="58">
         <f t="shared" si="0"/>
-        <v>83056.08</v>
+        <v>109473.08</v>
       </c>
       <c r="O14" s="59">
         <f t="shared" si="1"/>
-        <v>85548.08</v>
+        <v>112757.08</v>
       </c>
       <c r="P14" s="37">
         <f t="shared" si="7"/>
@@ -3723,35 +3716,35 @@
       </c>
       <c r="R14" s="37"/>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="149">
+      <c r="B15" s="118">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="C15" s="149" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="149" t="s">
-        <v>84</v>
+      <c r="C15" s="118" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="118" t="s">
+        <v>83</v>
       </c>
       <c r="E15" s="51">
         <v>7.59</v>
       </c>
       <c r="F15" s="52">
-        <v>272269.09000000003</v>
+        <v>670819.09</v>
       </c>
       <c r="G15" s="53">
-        <v>0</v>
+        <v>390520</v>
       </c>
       <c r="H15" s="54"/>
       <c r="I15" s="55">
         <f t="shared" si="2"/>
-        <v>272269.09000000003</v>
+        <v>280299.08999999997</v>
       </c>
       <c r="J15" s="55">
         <f t="shared" si="3"/>
-        <v>8031.9381550000016</v>
+        <v>8268.823155</v>
       </c>
       <c r="K15" s="56">
         <f t="shared" si="4"/>
@@ -3759,18 +3752,18 @@
       </c>
       <c r="L15" s="56">
         <f t="shared" si="5"/>
-        <v>390517.93925099989</v>
+        <v>514605.00260399998</v>
       </c>
       <c r="M15" s="57">
         <v>0</v>
       </c>
       <c r="N15" s="58">
         <f t="shared" si="0"/>
-        <v>670819.09</v>
+        <v>803173.09</v>
       </c>
       <c r="O15" s="59">
         <f t="shared" si="1"/>
-        <v>690944.09</v>
+        <v>827268.09</v>
       </c>
       <c r="P15" s="37">
         <f t="shared" si="7"/>
@@ -3778,35 +3771,36 @@
       </c>
       <c r="R15" s="37"/>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="166">
+      <c r="B16" s="118">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C16" s="166" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="166" t="s">
-        <v>85</v>
+      <c r="C16" s="118" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="118" t="s">
+        <v>84</v>
       </c>
       <c r="E16" s="51">
         <v>1.62</v>
       </c>
       <c r="F16" s="52">
-        <v>46384.1</v>
+        <v>131104.1</v>
       </c>
       <c r="G16" s="53">
-        <v>0</v>
+        <f>135040+46400</f>
+        <v>181440</v>
       </c>
       <c r="H16" s="54"/>
       <c r="I16" s="55">
         <f t="shared" si="2"/>
-        <v>46384.1</v>
+        <v>-50335.899999999994</v>
       </c>
       <c r="J16" s="55">
         <f t="shared" si="3"/>
-        <v>1368.33095</v>
+        <v>0</v>
       </c>
       <c r="K16" s="56">
         <f t="shared" si="4"/>
@@ -3814,45 +3808,45 @@
       </c>
       <c r="L16" s="56">
         <f t="shared" si="5"/>
-        <v>83351.65501799999</v>
+        <v>109836.64087200003</v>
       </c>
       <c r="M16" s="57">
         <v>0</v>
       </c>
       <c r="N16" s="58">
         <f t="shared" si="0"/>
-        <v>131104.1</v>
+        <v>59501.1</v>
       </c>
       <c r="O16" s="59">
         <f t="shared" si="1"/>
-        <v>135037.1</v>
+        <v>61286.1</v>
       </c>
       <c r="P16" s="37">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="Q16" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="R16" s="37"/>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="118">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="C17" s="48" t="s">
-        <v>115</v>
-      </c>
-      <c r="D17" s="48" t="s">
-        <v>86</v>
+      <c r="C17" s="118" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="118" t="s">
+        <v>85</v>
       </c>
       <c r="E17" s="51">
         <v>1.78</v>
       </c>
       <c r="F17" s="52">
-        <v>179205.11</v>
+        <v>276076.11</v>
       </c>
       <c r="G17" s="53">
         <v>0</v>
@@ -3860,11 +3854,11 @@
       <c r="H17" s="54"/>
       <c r="I17" s="55">
         <f t="shared" si="2"/>
-        <v>179205.11</v>
+        <v>276076.11</v>
       </c>
       <c r="J17" s="55">
         <f t="shared" si="3"/>
-        <v>5286.5507449999996</v>
+        <v>8144.2452450000001</v>
       </c>
       <c r="K17" s="56">
         <f t="shared" si="4"/>
@@ -3872,18 +3866,18 @@
       </c>
       <c r="L17" s="56">
         <f t="shared" si="5"/>
-        <v>91583.917241999981</v>
+        <v>120684.70416800001</v>
       </c>
       <c r="M17" s="57">
         <v>0</v>
       </c>
       <c r="N17" s="58">
         <f t="shared" si="0"/>
-        <v>276076.11</v>
+        <v>404905.11</v>
       </c>
       <c r="O17" s="59">
         <f t="shared" si="1"/>
-        <v>284358.11</v>
+        <v>417052.11</v>
       </c>
       <c r="P17" s="37">
         <f t="shared" si="7"/>
@@ -3891,23 +3885,23 @@
       </c>
       <c r="R17" s="37"/>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="118">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>86</v>
+      <c r="C18" s="118" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="118" t="s">
+        <v>85</v>
       </c>
       <c r="E18" s="51">
         <v>1.3</v>
       </c>
       <c r="F18" s="52">
-        <v>130933.12</v>
+        <v>201683.12</v>
       </c>
       <c r="G18" s="53">
         <v>0</v>
@@ -3915,11 +3909,11 @@
       <c r="H18" s="54"/>
       <c r="I18" s="55">
         <f t="shared" si="2"/>
-        <v>130933.12</v>
+        <v>201683.12</v>
       </c>
       <c r="J18" s="55">
         <f t="shared" si="3"/>
-        <v>3862.5270399999999</v>
+        <v>5949.6520399999999</v>
       </c>
       <c r="K18" s="56">
         <f t="shared" si="4"/>
@@ -3927,18 +3921,18 @@
       </c>
       <c r="L18" s="56">
         <f t="shared" si="5"/>
-        <v>66887.130569999994</v>
+        <v>88140.514280000018</v>
       </c>
       <c r="M18" s="57">
         <v>0</v>
       </c>
       <c r="N18" s="58">
         <f t="shared" si="0"/>
-        <v>201683.12</v>
+        <v>295773.12</v>
       </c>
       <c r="O18" s="59">
         <f t="shared" si="1"/>
-        <v>207733.12</v>
+        <v>304646.12</v>
       </c>
       <c r="P18" s="37">
         <f t="shared" si="7"/>
@@ -3946,27 +3940,27 @@
       </c>
       <c r="R18" s="37"/>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="118">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="C19" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="48" t="s">
-        <v>87</v>
+      <c r="C19" s="118" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="118" t="s">
+        <v>86</v>
       </c>
       <c r="E19" s="51">
         <v>1.38</v>
       </c>
       <c r="F19" s="52">
-        <v>49544.13</v>
+        <v>71003.13</v>
       </c>
       <c r="G19" s="53">
-        <f>116680.27-G20</f>
-        <v>49544.130000000005</v>
+        <f>F19</f>
+        <v>71003.13</v>
       </c>
       <c r="H19" s="54"/>
       <c r="I19" s="55">
@@ -3983,49 +3977,49 @@
       </c>
       <c r="L19" s="56">
         <f t="shared" si="5"/>
-        <v>71003.261681999982</v>
+        <v>93564.545928000007</v>
       </c>
       <c r="M19" s="57">
         <v>0</v>
       </c>
       <c r="N19" s="58">
         <f t="shared" si="0"/>
-        <v>71003.13</v>
+        <v>93565.13</v>
       </c>
       <c r="O19" s="59">
         <f t="shared" si="1"/>
-        <v>73133.13</v>
+        <v>96372.13</v>
       </c>
       <c r="P19" s="37">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
       <c r="Q19" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="R19" s="37"/>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="118">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="C20" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>87</v>
+      <c r="C20" s="118" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="118" t="s">
+        <v>86</v>
       </c>
       <c r="E20" s="51">
         <v>1.87</v>
       </c>
       <c r="F20" s="52">
-        <v>67136.14</v>
+        <v>96215.14</v>
       </c>
       <c r="G20" s="53">
         <f>F20</f>
-        <v>67136.14</v>
+        <v>96215.14</v>
       </c>
       <c r="H20" s="54"/>
       <c r="I20" s="55">
@@ -4042,57 +4036,57 @@
       </c>
       <c r="L20" s="56">
         <f t="shared" si="5"/>
-        <v>96214.564742999981</v>
+        <v>126786.73977200002</v>
       </c>
       <c r="M20" s="57">
         <v>0</v>
       </c>
       <c r="N20" s="58">
         <f t="shared" si="0"/>
-        <v>96215.14</v>
+        <v>126787.14</v>
       </c>
       <c r="O20" s="59">
         <f t="shared" si="1"/>
-        <v>99101.14</v>
+        <v>130591.14</v>
       </c>
       <c r="P20" s="37">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="Q20" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="R20" s="37"/>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="118">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C21" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>88</v>
+      <c r="C21" s="118" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="118" t="s">
+        <v>87</v>
       </c>
       <c r="E21" s="51">
         <v>2.91</v>
       </c>
       <c r="F21" s="52">
-        <v>775437.15</v>
+        <v>948037.15</v>
       </c>
       <c r="G21" s="53">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="H21" s="54"/>
       <c r="I21" s="55">
         <f t="shared" si="2"/>
-        <v>775437.15</v>
+        <v>798037.15</v>
       </c>
       <c r="J21" s="55">
         <f t="shared" si="3"/>
-        <v>22875.395925000001</v>
+        <v>23542.095925000001</v>
       </c>
       <c r="K21" s="56">
         <f t="shared" si="4"/>
@@ -4100,50 +4094,53 @@
       </c>
       <c r="L21" s="56">
         <f t="shared" si="5"/>
-        <v>149724.26919899997</v>
+        <v>197299.15119600002</v>
       </c>
       <c r="M21" s="57">
         <v>0</v>
       </c>
       <c r="N21" s="58">
         <f t="shared" si="0"/>
-        <v>948037.15</v>
+        <v>1018878.15</v>
       </c>
       <c r="O21" s="59">
         <f t="shared" si="1"/>
-        <v>976478.15</v>
+        <v>1049444.1499999999</v>
       </c>
       <c r="P21" s="37">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
+      <c r="Q21" t="s">
+        <v>198</v>
+      </c>
       <c r="R21" s="37"/>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="167"/>
-      <c r="B22" s="166">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="163"/>
+      <c r="B22" s="118">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C22" s="166" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="166" t="s">
-        <v>89</v>
+      <c r="C22" s="118" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="118" t="s">
+        <v>88</v>
       </c>
       <c r="E22" s="51">
         <v>2.14</v>
       </c>
       <c r="F22" s="52">
-        <v>73855.16</v>
+        <v>109962.16</v>
       </c>
       <c r="G22" s="53">
-        <v>74000</v>
+        <v>113300</v>
       </c>
       <c r="H22" s="54"/>
       <c r="I22" s="55">
         <f t="shared" si="2"/>
-        <v>-144.83999999999651</v>
+        <v>-3337.8399999999965</v>
       </c>
       <c r="J22" s="55">
         <f t="shared" si="3"/>
@@ -4155,55 +4152,55 @@
       </c>
       <c r="L22" s="56">
         <f t="shared" si="5"/>
-        <v>110106.50724599998</v>
+        <v>145092.84658400001</v>
       </c>
       <c r="M22" s="57">
         <v>0</v>
       </c>
       <c r="N22" s="58">
         <f t="shared" si="0"/>
-        <v>109962.16</v>
+        <v>141755.16</v>
       </c>
       <c r="O22" s="59">
         <f t="shared" si="1"/>
-        <v>113261.16</v>
+        <v>146008.16</v>
       </c>
       <c r="P22" s="37">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
       <c r="Q22" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="R22" s="37"/>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="181">
+      <c r="B23" s="118">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="C23" s="181" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="181" t="s">
-        <v>84</v>
+      <c r="C23" s="118" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="118" t="s">
+        <v>83</v>
       </c>
       <c r="E23" s="51">
         <v>0.89</v>
       </c>
       <c r="F23" s="52">
-        <v>31625.17</v>
+        <v>45717.17</v>
       </c>
       <c r="G23" s="53">
-        <v>31700</v>
+        <v>45800</v>
       </c>
       <c r="H23" s="54"/>
       <c r="I23" s="55">
         <f t="shared" si="2"/>
-        <v>-74.830000000001746</v>
+        <v>-82.830000000001746</v>
       </c>
       <c r="J23" s="55">
         <f t="shared" si="3"/>
@@ -4215,25 +4212,25 @@
       </c>
       <c r="L23" s="56">
         <f t="shared" si="5"/>
-        <v>45791.958620999991</v>
+        <v>60342.352084000006</v>
       </c>
       <c r="M23" s="57">
         <v>0</v>
       </c>
       <c r="N23" s="58">
         <f t="shared" si="0"/>
-        <v>45717.17</v>
+        <v>60260.17</v>
       </c>
       <c r="O23" s="59">
         <f t="shared" si="1"/>
-        <v>47089.17</v>
+        <v>62068.17</v>
       </c>
       <c r="P23" s="37">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>15</v>
       </c>
@@ -4242,16 +4239,16 @@
         <v>18</v>
       </c>
       <c r="C24" s="118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D24" s="118" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="119">
         <v>0.95</v>
       </c>
       <c r="F24" s="53">
-        <v>2719352.18</v>
+        <v>2848452.18</v>
       </c>
       <c r="G24" s="53">
         <v>0</v>
@@ -4259,11 +4256,11 @@
       <c r="H24" s="54"/>
       <c r="I24" s="55">
         <f t="shared" si="2"/>
-        <v>2719352.18</v>
+        <v>2848452.18</v>
       </c>
       <c r="J24" s="55">
         <f t="shared" si="3"/>
-        <v>80220.889310000013</v>
+        <v>84029.33931000001</v>
       </c>
       <c r="K24" s="56">
         <f t="shared" si="4"/>
@@ -4271,18 +4268,18 @@
       </c>
       <c r="L24" s="56">
         <f t="shared" si="5"/>
-        <v>48879.056954999985</v>
+        <v>64410.375820000001</v>
       </c>
       <c r="M24" s="57">
         <v>0</v>
       </c>
       <c r="N24" s="58">
         <f t="shared" si="0"/>
-        <v>2848452.18</v>
+        <v>2996892.18</v>
       </c>
       <c r="O24" s="59">
         <f t="shared" si="1"/>
-        <v>2933906.18</v>
+        <v>3086799.18</v>
       </c>
       <c r="P24" s="37">
         <f t="shared" si="7"/>
@@ -4291,7 +4288,7 @@
       <c r="Q24" s="105"/>
       <c r="R24" s="104"/>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>16</v>
       </c>
@@ -4299,25 +4296,25 @@
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="C25" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="48" t="s">
-        <v>84</v>
+      <c r="C25" s="118" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" s="118" t="s">
+        <v>83</v>
       </c>
       <c r="E25" s="51">
         <v>1.94</v>
       </c>
       <c r="F25" s="52">
-        <v>60570.19</v>
+        <v>99586.19</v>
       </c>
       <c r="G25" s="53">
-        <v>60800</v>
+        <v>100000</v>
       </c>
       <c r="H25" s="54"/>
       <c r="I25" s="55">
         <f t="shared" si="2"/>
-        <v>-229.80999999999767</v>
+        <v>-413.80999999999767</v>
       </c>
       <c r="J25" s="55">
         <f t="shared" si="3"/>
@@ -4329,25 +4326,25 @@
       </c>
       <c r="L25" s="56">
         <f t="shared" si="5"/>
-        <v>99816.179465999972</v>
+        <v>131532.767464</v>
       </c>
       <c r="M25" s="57">
         <v>0</v>
       </c>
       <c r="N25" s="58">
         <f t="shared" si="0"/>
-        <v>99586.19</v>
+        <v>131119.19</v>
       </c>
       <c r="O25" s="59">
         <f t="shared" si="1"/>
-        <v>102574.19</v>
+        <v>135053.19</v>
       </c>
       <c r="P25" s="37">
         <f t="shared" si="7"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>16</v>
       </c>
@@ -4355,29 +4352,29 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="C26" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>91</v>
+      <c r="C26" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="118" t="s">
+        <v>90</v>
       </c>
       <c r="E26" s="51">
         <v>1.84</v>
       </c>
       <c r="F26" s="52">
-        <v>66059.199999999997</v>
+        <v>162679.20000000001</v>
       </c>
       <c r="G26" s="53">
-        <v>0</v>
+        <v>94671.2</v>
       </c>
       <c r="H26" s="54"/>
       <c r="I26" s="55">
         <f t="shared" si="2"/>
-        <v>66059.199999999997</v>
+        <v>68008.000000000015</v>
       </c>
       <c r="J26" s="55">
         <f t="shared" si="3"/>
-        <v>1948.7464</v>
+        <v>2006.2360000000006</v>
       </c>
       <c r="K26" s="56">
         <f t="shared" si="4"/>
@@ -4385,25 +4382,25 @@
       </c>
       <c r="L26" s="56">
         <f t="shared" si="5"/>
-        <v>94671.015575999976</v>
+        <v>124752.72790400001</v>
       </c>
       <c r="M26" s="57">
         <v>0</v>
       </c>
       <c r="N26" s="58">
         <f t="shared" si="0"/>
-        <v>162679.20000000001</v>
+        <v>194767.2</v>
       </c>
       <c r="O26" s="59">
         <f t="shared" si="1"/>
-        <v>167559.20000000001</v>
+        <v>200610.2</v>
       </c>
       <c r="P26" s="37">
         <f t="shared" si="7"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>17</v>
       </c>
@@ -4411,29 +4408,29 @@
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="118">
         <v>1106</v>
       </c>
-      <c r="D27" s="48" t="s">
-        <v>92</v>
+      <c r="D27" s="118" t="s">
+        <v>91</v>
       </c>
       <c r="E27" s="51">
         <v>5.12</v>
       </c>
       <c r="F27" s="52">
-        <v>6079224.21</v>
+        <v>5904294.21</v>
       </c>
       <c r="G27" s="53">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="H27" s="54"/>
       <c r="I27" s="55">
         <f t="shared" si="2"/>
-        <v>5479224.21</v>
+        <v>5904294.21</v>
       </c>
       <c r="J27" s="55">
         <f t="shared" si="3"/>
-        <v>161637.114195</v>
+        <v>174176.679195</v>
       </c>
       <c r="K27" s="56">
         <f t="shared" si="4"/>
@@ -4441,25 +4438,25 @@
       </c>
       <c r="L27" s="56">
         <f t="shared" si="5"/>
-        <v>263432.39116799994</v>
+        <v>347138.02547200007</v>
       </c>
       <c r="M27" s="57">
         <v>0</v>
       </c>
       <c r="N27" s="58">
         <f t="shared" si="0"/>
-        <v>5904294.21</v>
+        <v>6425609.21</v>
       </c>
       <c r="O27" s="59">
         <f t="shared" si="1"/>
-        <v>6081423.21</v>
+        <v>6618377.21</v>
       </c>
       <c r="P27" s="37">
         <f t="shared" si="7"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>17</v>
       </c>
@@ -4467,26 +4464,25 @@
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="C28" s="48">
+      <c r="C28" s="118">
         <v>1101</v>
       </c>
-      <c r="D28" s="48" t="s">
-        <v>84</v>
+      <c r="D28" s="118" t="s">
+        <v>83</v>
       </c>
       <c r="E28" s="51">
         <v>3.88</v>
       </c>
       <c r="F28" s="52">
-        <v>139195.22</v>
+        <v>198828.22</v>
       </c>
       <c r="G28" s="53">
-        <f>140000</f>
-        <v>140000</v>
+        <v>200000</v>
       </c>
       <c r="H28" s="54"/>
       <c r="I28" s="55">
         <f t="shared" si="2"/>
-        <v>-804.77999999999884</v>
+        <v>-1171.7799999999988</v>
       </c>
       <c r="J28" s="55">
         <f t="shared" si="3"/>
@@ -4498,28 +4494,28 @@
       </c>
       <c r="L28" s="56">
         <f t="shared" si="5"/>
-        <v>199632.35893199994</v>
+        <v>263065.53492800001</v>
       </c>
       <c r="M28" s="57">
         <v>0</v>
       </c>
       <c r="N28" s="58">
         <f t="shared" si="0"/>
-        <v>198828.22</v>
+        <v>261894.22</v>
       </c>
       <c r="O28" s="59">
         <f t="shared" si="1"/>
-        <v>204793.22</v>
+        <v>269751.21999999997</v>
       </c>
       <c r="P28" s="37">
         <f t="shared" si="7"/>
         <v>0.22000000000000006</v>
       </c>
       <c r="Q28" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>18</v>
       </c>
@@ -4527,21 +4523,21 @@
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="118">
         <v>1102</v>
       </c>
-      <c r="D29" s="48" t="s">
-        <v>93</v>
+      <c r="D29" s="118" t="s">
+        <v>92</v>
       </c>
       <c r="E29" s="51">
         <v>0.92</v>
       </c>
       <c r="F29" s="52">
-        <v>32615.23</v>
+        <v>48756.23</v>
       </c>
       <c r="G29" s="53">
         <f>F29</f>
-        <v>32615.23</v>
+        <v>48756.23</v>
       </c>
       <c r="H29" s="54"/>
       <c r="I29" s="55">
@@ -4558,25 +4554,25 @@
       </c>
       <c r="L29" s="56">
         <f t="shared" si="5"/>
-        <v>47335.507787999988</v>
+        <v>62376.363952000007</v>
       </c>
       <c r="M29" s="57">
         <v>0</v>
       </c>
       <c r="N29" s="58">
         <f t="shared" si="0"/>
-        <v>47336.23</v>
+        <v>62376.23</v>
       </c>
       <c r="O29" s="59">
         <f t="shared" si="1"/>
-        <v>48756.23</v>
+        <v>64247.23</v>
       </c>
       <c r="P29" s="37">
         <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>18</v>
       </c>
@@ -4584,17 +4580,17 @@
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="C30" s="48">
+      <c r="C30" s="118">
         <v>1103</v>
       </c>
-      <c r="D30" s="48" t="s">
-        <v>94</v>
+      <c r="D30" s="118" t="s">
+        <v>93</v>
       </c>
       <c r="E30" s="51">
         <v>1.43</v>
       </c>
       <c r="F30" s="52">
-        <v>4589850.24</v>
+        <v>4798827.24</v>
       </c>
       <c r="G30" s="53">
         <v>0</v>
@@ -4602,11 +4598,11 @@
       <c r="H30" s="54"/>
       <c r="I30" s="55">
         <f t="shared" si="2"/>
-        <v>4589850.24</v>
+        <v>4798827.24</v>
       </c>
       <c r="J30" s="55">
         <f t="shared" si="3"/>
-        <v>135400.58208000002</v>
+        <v>141565.40358000001</v>
       </c>
       <c r="K30" s="56">
         <f t="shared" si="4"/>
@@ -4614,25 +4610,25 @@
       </c>
       <c r="L30" s="56">
         <f t="shared" si="5"/>
-        <v>73575.84362699998</v>
+        <v>96954.565708000009</v>
       </c>
       <c r="M30" s="57">
         <v>0</v>
       </c>
       <c r="N30" s="58">
         <f t="shared" si="0"/>
-        <v>4798827.24</v>
+        <v>5037347.24</v>
       </c>
       <c r="O30" s="59">
         <f t="shared" si="1"/>
-        <v>4942792.24</v>
+        <v>5188467.24</v>
       </c>
       <c r="P30" s="37">
         <f t="shared" si="7"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>19</v>
       </c>
@@ -4640,29 +4636,29 @@
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="C31" s="48">
+      <c r="C31" s="118">
         <v>1104</v>
       </c>
-      <c r="D31" s="48" t="s">
-        <v>95</v>
+      <c r="D31" s="118" t="s">
+        <v>94</v>
       </c>
       <c r="E31" s="51">
         <v>2.19</v>
       </c>
       <c r="F31" s="52">
-        <v>78625.25</v>
+        <v>193624.25</v>
       </c>
       <c r="G31" s="53">
-        <v>0</v>
+        <v>199433.25</v>
       </c>
       <c r="H31" s="54"/>
       <c r="I31" s="55">
         <f t="shared" si="2"/>
-        <v>78625.25</v>
+        <v>-5809</v>
       </c>
       <c r="J31" s="55">
         <f t="shared" si="3"/>
-        <v>2319.4448750000001</v>
+        <v>0</v>
       </c>
       <c r="K31" s="56">
         <f t="shared" si="4"/>
@@ -4670,25 +4666,25 @@
       </c>
       <c r="L31" s="56">
         <f t="shared" si="5"/>
-        <v>112679.08919099996</v>
+        <v>148482.86636400002</v>
       </c>
       <c r="M31" s="57">
         <v>0</v>
       </c>
       <c r="N31" s="58">
         <f t="shared" si="0"/>
-        <v>193624.25</v>
+        <v>142674.25</v>
       </c>
       <c r="O31" s="59">
         <f t="shared" si="1"/>
-        <v>199433.25</v>
+        <v>146954.25</v>
       </c>
       <c r="P31" s="37">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>19</v>
       </c>
@@ -4696,17 +4692,17 @@
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
-      <c r="C32" s="48">
+      <c r="C32" s="118">
         <v>1105</v>
       </c>
-      <c r="D32" s="48" t="s">
-        <v>96</v>
+      <c r="D32" s="118" t="s">
+        <v>95</v>
       </c>
       <c r="E32" s="51">
         <v>1.94</v>
       </c>
       <c r="F32" s="52">
-        <v>-62054.81</v>
+        <v>37761.26</v>
       </c>
       <c r="G32" s="53">
         <v>0</v>
@@ -4714,11 +4710,11 @@
       <c r="H32" s="54"/>
       <c r="I32" s="55">
         <f t="shared" si="2"/>
-        <v>-62054.81</v>
+        <v>37761.26</v>
       </c>
       <c r="J32" s="55">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1113.9571700000001</v>
       </c>
       <c r="K32" s="56">
         <f t="shared" si="4"/>
@@ -4726,25 +4722,25 @@
       </c>
       <c r="L32" s="56">
         <f t="shared" si="5"/>
-        <v>99816.179465999972</v>
+        <v>131532.767464</v>
       </c>
       <c r="M32" s="57">
         <v>0</v>
       </c>
       <c r="N32" s="58">
         <f t="shared" si="0"/>
-        <v>37761.26</v>
+        <v>170408.26</v>
       </c>
       <c r="O32" s="59">
         <f t="shared" si="1"/>
-        <v>38894.26</v>
+        <v>175520.26</v>
       </c>
       <c r="P32" s="37">
         <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>20</v>
       </c>
@@ -4752,26 +4748,25 @@
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="C33" s="48">
+      <c r="C33" s="118">
         <v>2206</v>
       </c>
-      <c r="D33" s="48" t="s">
-        <v>97</v>
+      <c r="D33" s="118" t="s">
+        <v>96</v>
       </c>
       <c r="E33" s="51">
         <v>2.17</v>
       </c>
       <c r="F33" s="52">
-        <v>77907.27</v>
+        <v>111650.27</v>
       </c>
       <c r="G33" s="53">
-        <f>77907.27</f>
-        <v>77907.27</v>
+        <v>115000.27</v>
       </c>
       <c r="H33" s="54"/>
       <c r="I33" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3350</v>
       </c>
       <c r="J33" s="55">
         <f t="shared" si="3"/>
@@ -4783,18 +4778,18 @@
       </c>
       <c r="L33" s="56">
         <f t="shared" si="5"/>
-        <v>111650.05641299997</v>
+        <v>147126.85845200001</v>
       </c>
       <c r="M33" s="57">
         <v>0</v>
       </c>
       <c r="N33" s="58">
         <f t="shared" si="0"/>
-        <v>111650.27</v>
+        <v>143777.26999999999</v>
       </c>
       <c r="O33" s="59">
         <f t="shared" si="1"/>
-        <v>115000.27</v>
+        <v>148090.26999999999</v>
       </c>
       <c r="P33" s="37">
         <f t="shared" si="7"/>
@@ -4802,7 +4797,7 @@
       </c>
       <c r="R33" s="36"/>
     </row>
-    <row r="34" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>20</v>
       </c>
@@ -4810,25 +4805,26 @@
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="C34" s="48">
+      <c r="C34" s="118">
         <v>2207</v>
       </c>
-      <c r="D34" s="48" t="s">
-        <v>98</v>
+      <c r="D34" s="118" t="s">
+        <v>97</v>
       </c>
       <c r="E34" s="51">
         <v>1.23</v>
       </c>
       <c r="F34" s="53">
-        <v>36627.279999999999</v>
+        <v>63283.28</v>
       </c>
       <c r="G34" s="53">
-        <v>36630</v>
+        <f>21000+44100</f>
+        <v>65100</v>
       </c>
       <c r="H34" s="54"/>
       <c r="I34" s="55">
         <f t="shared" si="2"/>
-        <v>-2.7200000000011642</v>
+        <v>-1816.7200000000012</v>
       </c>
       <c r="J34" s="55">
         <f t="shared" si="3"/>
@@ -4840,28 +4836,28 @@
       </c>
       <c r="L34" s="56">
         <f t="shared" si="5"/>
-        <v>63285.515846999988</v>
+        <v>83394.486588000014</v>
       </c>
       <c r="M34" s="57">
         <v>0</v>
       </c>
       <c r="N34" s="58">
         <f t="shared" si="0"/>
-        <v>63283.28</v>
+        <v>81578.28</v>
       </c>
       <c r="O34" s="59">
         <f t="shared" si="1"/>
-        <v>65181.279999999999</v>
+        <v>84025.279999999999</v>
       </c>
       <c r="P34" s="37">
         <f t="shared" si="7"/>
         <v>0.28000000000000008</v>
       </c>
       <c r="Q34" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>21</v>
       </c>
@@ -4869,26 +4865,26 @@
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="C35" s="48">
+      <c r="C35" s="118">
         <v>2208</v>
       </c>
-      <c r="D35" s="48" t="s">
-        <v>99</v>
+      <c r="D35" s="118" t="s">
+        <v>98</v>
       </c>
       <c r="E35" s="51">
         <v>1.29</v>
       </c>
       <c r="F35" s="52">
-        <v>46313.29</v>
+        <v>66359.289999999994</v>
       </c>
       <c r="G35" s="53">
-        <f>95500-G36</f>
-        <v>46326.7</v>
+        <f>F35</f>
+        <v>66359.289999999994</v>
       </c>
       <c r="H35" s="54"/>
       <c r="I35" s="55">
         <f t="shared" si="2"/>
-        <v>-13.409999999996217</v>
+        <v>0</v>
       </c>
       <c r="J35" s="55">
         <f t="shared" si="3"/>
@@ -4900,25 +4896,25 @@
       </c>
       <c r="L35" s="56">
         <f t="shared" si="5"/>
-        <v>66372.614180999983</v>
+        <v>87462.510324000003</v>
       </c>
       <c r="M35" s="57">
         <v>0</v>
       </c>
       <c r="N35" s="58">
         <f t="shared" si="0"/>
-        <v>66359.289999999994</v>
+        <v>87463.29</v>
       </c>
       <c r="O35" s="59">
         <f t="shared" si="1"/>
-        <v>68350.289999999994</v>
+        <v>90087.29</v>
       </c>
       <c r="P35" s="37">
         <f t="shared" si="7"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>21</v>
       </c>
@@ -4926,21 +4922,21 @@
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="C36" s="48">
+      <c r="C36" s="118">
         <v>2201</v>
       </c>
-      <c r="D36" s="48" t="s">
-        <v>99</v>
+      <c r="D36" s="118" t="s">
+        <v>98</v>
       </c>
       <c r="E36" s="51">
         <v>1.36</v>
       </c>
       <c r="F36" s="52">
-        <v>49173.3</v>
+        <v>69974.3</v>
       </c>
       <c r="G36" s="53">
         <f>F36</f>
-        <v>49173.3</v>
+        <v>69974.3</v>
       </c>
       <c r="H36" s="54"/>
       <c r="I36" s="55">
@@ -4957,25 +4953,25 @@
       </c>
       <c r="L36" s="56">
         <f t="shared" si="5"/>
-        <v>69974.228903999989</v>
+        <v>92208.53801600002</v>
       </c>
       <c r="M36" s="57">
         <v>0</v>
       </c>
       <c r="N36" s="58">
         <f t="shared" si="0"/>
-        <v>69974.3</v>
+        <v>92209.3</v>
       </c>
       <c r="O36" s="59">
         <f t="shared" si="1"/>
-        <v>72073.3</v>
+        <v>94975.3</v>
       </c>
       <c r="P36" s="37">
         <f t="shared" si="7"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>22</v>
       </c>
@@ -4983,30 +4979,27 @@
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="C37" s="48">
+      <c r="C37" s="118">
         <v>2202</v>
       </c>
-      <c r="D37" s="48" t="s">
-        <v>100</v>
+      <c r="D37" s="118" t="s">
+        <v>99</v>
       </c>
       <c r="E37" s="51">
         <v>0.57999999999999996</v>
       </c>
       <c r="F37" s="53">
-        <v>20823.310000000001</v>
-      </c>
-      <c r="G37" s="53">
-        <f>150429.3-G38-G40-G39</f>
-        <v>20823.309999999983</v>
-      </c>
+        <v>29842.31</v>
+      </c>
+      <c r="G37" s="53"/>
       <c r="H37" s="54"/>
       <c r="I37" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>29842.31</v>
       </c>
       <c r="J37" s="55">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>880.34814500000005</v>
       </c>
       <c r="K37" s="56">
         <f t="shared" si="4"/>
@@ -5014,28 +5007,28 @@
       </c>
       <c r="L37" s="56">
         <f t="shared" si="5"/>
-        <v>29841.950561999991</v>
+        <v>39324.229447999998</v>
       </c>
       <c r="M37" s="57">
         <v>0</v>
       </c>
       <c r="N37" s="58">
         <f t="shared" si="0"/>
-        <v>29842.31</v>
+        <v>70047.31</v>
       </c>
       <c r="O37" s="59">
         <f t="shared" si="1"/>
-        <v>30737.31</v>
+        <v>72148.31</v>
       </c>
       <c r="P37" s="37">
         <f t="shared" si="7"/>
         <v>0.31000000000000011</v>
       </c>
       <c r="Q37" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>23</v>
       </c>
@@ -5043,30 +5036,27 @@
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
-      <c r="C38" s="48">
+      <c r="C38" s="118">
         <v>2203</v>
       </c>
-      <c r="D38" s="48" t="s">
-        <v>100</v>
+      <c r="D38" s="118" t="s">
+        <v>99</v>
       </c>
       <c r="E38" s="51">
         <v>0.57999999999999996</v>
       </c>
       <c r="F38" s="52">
-        <v>20823.32</v>
-      </c>
-      <c r="G38" s="53">
-        <f>F38</f>
-        <v>20823.32</v>
-      </c>
+        <v>29842.32</v>
+      </c>
+      <c r="G38" s="53"/>
       <c r="H38" s="54"/>
       <c r="I38" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>29842.32</v>
       </c>
       <c r="J38" s="55">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>880.3484400000001</v>
       </c>
       <c r="K38" s="56">
         <f t="shared" si="4"/>
@@ -5074,28 +5064,28 @@
       </c>
       <c r="L38" s="56">
         <f t="shared" si="5"/>
-        <v>29841.950561999991</v>
+        <v>39324.229447999998</v>
       </c>
       <c r="M38" s="57">
         <v>0</v>
       </c>
       <c r="N38" s="58">
         <f t="shared" si="0"/>
-        <v>29842.32</v>
+        <v>70047.320000000007</v>
       </c>
       <c r="O38" s="59">
         <f t="shared" si="1"/>
-        <v>30737.32</v>
+        <v>72148.320000000007</v>
       </c>
       <c r="P38" s="37">
         <f t="shared" si="7"/>
         <v>0.32000000000000012</v>
       </c>
       <c r="Q38" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>24</v>
       </c>
@@ -5103,26 +5093,25 @@
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
-      <c r="C39" s="48">
+      <c r="C39" s="118">
         <v>2204</v>
       </c>
-      <c r="D39" s="48" t="s">
-        <v>101</v>
+      <c r="D39" s="118" t="s">
+        <v>100</v>
       </c>
       <c r="E39" s="51">
         <v>1.36</v>
       </c>
       <c r="F39" s="52">
-        <v>48826.33</v>
+        <v>69974.33</v>
       </c>
       <c r="G39" s="53">
-        <f>F39</f>
-        <v>48826.33</v>
+        <v>72073.33</v>
       </c>
       <c r="H39" s="54"/>
       <c r="I39" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-2099</v>
       </c>
       <c r="J39" s="55">
         <f t="shared" si="3"/>
@@ -5134,28 +5123,28 @@
       </c>
       <c r="L39" s="56">
         <f t="shared" si="5"/>
-        <v>69974.228903999989</v>
+        <v>92208.53801600002</v>
       </c>
       <c r="M39" s="57">
         <v>0</v>
       </c>
       <c r="N39" s="58">
         <f t="shared" si="0"/>
-        <v>69974.33</v>
+        <v>90110.33</v>
       </c>
       <c r="O39" s="59">
         <f t="shared" si="1"/>
-        <v>72073.33</v>
+        <v>92813.33</v>
       </c>
       <c r="P39" s="37">
         <f t="shared" si="7"/>
         <v>0.33000000000000013</v>
       </c>
       <c r="Q39" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>25</v>
       </c>
@@ -5163,30 +5152,27 @@
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="118">
         <v>2205</v>
       </c>
-      <c r="D40" s="48" t="s">
-        <v>100</v>
+      <c r="D40" s="118" t="s">
+        <v>99</v>
       </c>
       <c r="E40" s="51">
         <v>1.67</v>
       </c>
       <c r="F40" s="52">
-        <v>59956.34</v>
-      </c>
-      <c r="G40" s="53">
-        <f>F40</f>
-        <v>59956.34</v>
-      </c>
+        <v>85924.34</v>
+      </c>
+      <c r="G40" s="53"/>
       <c r="H40" s="54"/>
       <c r="I40" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>85924.34</v>
       </c>
       <c r="J40" s="55">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2534.7680300000002</v>
       </c>
       <c r="K40" s="56">
         <f t="shared" si="4"/>
@@ -5194,28 +5180,28 @@
       </c>
       <c r="L40" s="56">
         <f t="shared" si="5"/>
-        <v>85924.236962999974</v>
+        <v>113226.66065200001</v>
       </c>
       <c r="M40" s="57">
         <v>0</v>
       </c>
       <c r="N40" s="58">
         <f t="shared" si="0"/>
-        <v>85924.34</v>
+        <v>201686.34</v>
       </c>
       <c r="O40" s="59">
         <f t="shared" si="1"/>
-        <v>88502.34</v>
+        <v>207737.34</v>
       </c>
       <c r="P40" s="37">
         <f t="shared" si="7"/>
         <v>0.34000000000000014</v>
       </c>
       <c r="Q40" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>27</v>
       </c>
@@ -5223,26 +5209,26 @@
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="C41" s="48">
+      <c r="C41" s="118">
         <v>2206</v>
       </c>
-      <c r="D41" s="48" t="s">
-        <v>102</v>
+      <c r="D41" s="118" t="s">
+        <v>101</v>
       </c>
       <c r="E41" s="51">
         <v>2.17</v>
       </c>
       <c r="F41" s="52">
-        <v>77907.350000000006</v>
+        <v>111650.35</v>
       </c>
       <c r="G41" s="53">
-        <f>122066.71-G42</f>
-        <v>77907.350000000006</v>
+        <f>180185.71-G42</f>
+        <v>116899.34999999999</v>
       </c>
       <c r="H41" s="54"/>
       <c r="I41" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-5248.9999999999854</v>
       </c>
       <c r="J41" s="55">
         <f t="shared" si="3"/>
@@ -5254,28 +5240,28 @@
       </c>
       <c r="L41" s="56">
         <f t="shared" si="5"/>
-        <v>111650.05641299997</v>
+        <v>147126.85845200001</v>
       </c>
       <c r="M41" s="57">
         <v>0</v>
       </c>
       <c r="N41" s="58">
         <f t="shared" si="0"/>
-        <v>111650.35</v>
+        <v>141878.35</v>
       </c>
       <c r="O41" s="59">
         <f t="shared" si="1"/>
-        <v>115000.35</v>
+        <v>146134.35</v>
       </c>
       <c r="P41" s="37">
         <f t="shared" si="7"/>
         <v>0.35000000000000014</v>
       </c>
       <c r="Q41" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>27</v>
       </c>
@@ -5283,21 +5269,21 @@
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="C42" s="48">
+      <c r="C42" s="118">
         <v>2207</v>
       </c>
-      <c r="D42" s="48" t="s">
-        <v>102</v>
+      <c r="D42" s="118" t="s">
+        <v>101</v>
       </c>
       <c r="E42" s="51">
         <v>1.23</v>
       </c>
       <c r="F42" s="52">
-        <v>44159.360000000001</v>
+        <v>63286.36</v>
       </c>
       <c r="G42" s="53">
         <f>F42</f>
-        <v>44159.360000000001</v>
+        <v>63286.36</v>
       </c>
       <c r="H42" s="54"/>
       <c r="I42" s="55">
@@ -5314,28 +5300,28 @@
       </c>
       <c r="L42" s="56">
         <f t="shared" si="5"/>
-        <v>63285.515846999988</v>
+        <v>83394.486588000014</v>
       </c>
       <c r="M42" s="57">
         <v>0</v>
       </c>
       <c r="N42" s="58">
         <f t="shared" si="0"/>
-        <v>63286.36</v>
+        <v>83394.36</v>
       </c>
       <c r="O42" s="59">
         <f t="shared" si="1"/>
-        <v>65185.36</v>
+        <v>85896.36</v>
       </c>
       <c r="P42" s="37">
         <f t="shared" si="7"/>
         <v>0.36000000000000015</v>
       </c>
       <c r="Q42" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>27</v>
       </c>
@@ -5343,30 +5329,27 @@
         <f t="shared" si="6"/>
         <v>37</v>
       </c>
-      <c r="C43" s="48">
+      <c r="C43" s="118">
         <v>3308</v>
       </c>
-      <c r="D43" s="48" t="s">
-        <v>125</v>
+      <c r="D43" s="118" t="s">
+        <v>124</v>
       </c>
       <c r="E43" s="51">
         <v>1.23</v>
       </c>
       <c r="F43" s="52">
-        <v>46313.37</v>
-      </c>
-      <c r="G43" s="53">
-        <f>F43</f>
-        <v>46313.37</v>
-      </c>
+        <v>63286.37</v>
+      </c>
+      <c r="G43" s="53"/>
       <c r="H43" s="54"/>
       <c r="I43" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>63286.37</v>
       </c>
       <c r="J43" s="55">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1866.9479150000002</v>
       </c>
       <c r="K43" s="56">
         <f t="shared" si="4"/>
@@ -5374,18 +5357,18 @@
       </c>
       <c r="L43" s="56">
         <f t="shared" si="5"/>
-        <v>63285.515846999988</v>
+        <v>83394.486588000014</v>
       </c>
       <c r="M43" s="57">
         <v>0</v>
       </c>
       <c r="N43" s="58">
         <f t="shared" si="0"/>
-        <v>63286.37</v>
+        <v>148548.37</v>
       </c>
       <c r="O43" s="59">
         <f t="shared" si="1"/>
-        <v>65185.37</v>
+        <v>153004.37</v>
       </c>
       <c r="P43" s="37">
         <f t="shared" si="7"/>
@@ -5393,7 +5376,7 @@
       </c>
       <c r="Q43" s="104"/>
     </row>
-    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>27</v>
       </c>
@@ -5401,17 +5384,17 @@
         <f t="shared" si="6"/>
         <v>38</v>
       </c>
-      <c r="C44" s="48">
+      <c r="C44" s="118">
         <v>3301</v>
       </c>
-      <c r="D44" s="138" t="s">
-        <v>126</v>
+      <c r="D44" s="226" t="s">
+        <v>125</v>
       </c>
       <c r="E44" s="51">
         <v>1.36</v>
       </c>
       <c r="F44" s="52">
-        <v>258817.38</v>
+        <v>336427.38</v>
       </c>
       <c r="G44" s="53">
         <v>0</v>
@@ -5419,11 +5402,11 @@
       <c r="H44" s="54"/>
       <c r="I44" s="55">
         <f t="shared" si="2"/>
-        <v>258817.38</v>
+        <v>336427.38</v>
       </c>
       <c r="J44" s="55">
         <f t="shared" si="3"/>
-        <v>7635.1127100000003</v>
+        <v>9924.6077100000002</v>
       </c>
       <c r="K44" s="56">
         <f t="shared" si="4"/>
@@ -5431,25 +5414,25 @@
       </c>
       <c r="L44" s="56">
         <f t="shared" si="5"/>
-        <v>69974.228903999989</v>
+        <v>92208.53801600002</v>
       </c>
       <c r="M44" s="57">
         <v>0</v>
       </c>
       <c r="N44" s="58">
         <f t="shared" si="0"/>
-        <v>336427.38</v>
+        <v>438561.38</v>
       </c>
       <c r="O44" s="59">
         <f t="shared" si="1"/>
-        <v>346520.38</v>
+        <v>451718.38</v>
       </c>
       <c r="P44" s="37">
         <f t="shared" si="7"/>
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>27</v>
       </c>
@@ -5457,26 +5440,25 @@
         <f>B44+1</f>
         <v>39</v>
       </c>
-      <c r="C45" s="48">
+      <c r="C45" s="118">
         <v>3302</v>
       </c>
-      <c r="D45" s="48" t="s">
-        <v>103</v>
+      <c r="D45" s="118" t="s">
+        <v>102</v>
       </c>
       <c r="E45" s="51">
         <v>0.57999999999999996</v>
       </c>
       <c r="F45" s="52">
-        <v>21612.39</v>
+        <v>29842.39</v>
       </c>
       <c r="G45" s="53">
-        <f>F45</f>
-        <v>21612.39</v>
+        <v>30737.39</v>
       </c>
       <c r="H45" s="61"/>
       <c r="I45" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-895</v>
       </c>
       <c r="J45" s="55">
         <f t="shared" si="3"/>
@@ -5488,49 +5470,48 @@
       </c>
       <c r="L45" s="56">
         <f t="shared" si="5"/>
-        <v>29841.950561999991</v>
+        <v>39324.229447999998</v>
       </c>
       <c r="M45" s="57">
         <v>0</v>
       </c>
       <c r="N45" s="58">
         <f t="shared" si="0"/>
-        <v>29842.39</v>
+        <v>38429.39</v>
       </c>
       <c r="O45" s="59">
         <f t="shared" si="1"/>
-        <v>30737.39</v>
+        <v>39582.39</v>
       </c>
       <c r="P45" s="37">
         <f t="shared" si="7"/>
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B46" s="118">
         <f t="shared" ref="B46:B64" si="8">B45+1</f>
         <v>40</v>
       </c>
-      <c r="C46" s="48">
+      <c r="C46" s="118">
         <v>3303</v>
       </c>
-      <c r="D46" s="48" t="s">
-        <v>103</v>
+      <c r="D46" s="118" t="s">
+        <v>102</v>
       </c>
       <c r="E46" s="51">
         <v>0.57999999999999996</v>
       </c>
       <c r="F46" s="52">
-        <v>21612.400000000001</v>
+        <v>29842.400000000001</v>
       </c>
       <c r="G46" s="53">
-        <f>F46</f>
-        <v>21612.400000000001</v>
+        <v>30737.4</v>
       </c>
       <c r="H46" s="61"/>
       <c r="I46" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-895</v>
       </c>
       <c r="J46" s="55">
         <f t="shared" si="3"/>
@@ -5542,52 +5523,53 @@
       </c>
       <c r="L46" s="56">
         <f t="shared" si="5"/>
-        <v>29841.950561999991</v>
+        <v>39324.229447999998</v>
       </c>
       <c r="M46" s="57">
         <v>0</v>
       </c>
       <c r="N46" s="58">
         <f t="shared" si="0"/>
-        <v>29842.400000000001</v>
+        <v>38429.4</v>
       </c>
       <c r="O46" s="59">
         <f t="shared" si="1"/>
-        <v>30737.4</v>
+        <v>39582.400000000001</v>
       </c>
       <c r="P46" s="37">
         <f t="shared" si="7"/>
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B47" s="157">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B47" s="118">
         <f t="shared" si="8"/>
         <v>41</v>
       </c>
-      <c r="C47" s="157">
+      <c r="C47" s="118">
         <v>3304</v>
       </c>
-      <c r="D47" s="157" t="s">
-        <v>143</v>
+      <c r="D47" s="118" t="s">
+        <v>133</v>
       </c>
       <c r="E47" s="51">
         <v>1.36</v>
       </c>
       <c r="F47" s="52">
-        <v>48548.41</v>
+        <v>119955.41</v>
       </c>
       <c r="G47" s="53">
-        <v>0</v>
+        <f>50000+70000</f>
+        <v>120000</v>
       </c>
       <c r="H47" s="61"/>
       <c r="I47" s="55">
         <f t="shared" si="2"/>
-        <v>48548.41</v>
+        <v>-44.589999999996508</v>
       </c>
       <c r="J47" s="55">
         <f t="shared" si="3"/>
-        <v>1432.1780950000002</v>
+        <v>0</v>
       </c>
       <c r="K47" s="56">
         <f t="shared" si="4"/>
@@ -5595,40 +5577,40 @@
       </c>
       <c r="L47" s="56">
         <f t="shared" si="5"/>
-        <v>69974.228903999989</v>
+        <v>92208.53801600002</v>
       </c>
       <c r="M47" s="57">
         <v>0</v>
       </c>
       <c r="N47" s="58">
         <f t="shared" si="0"/>
-        <v>119955.41</v>
+        <v>92164.41</v>
       </c>
       <c r="O47" s="59">
         <f t="shared" si="1"/>
-        <v>123554.41</v>
+        <v>94929.41</v>
       </c>
       <c r="P47" s="37">
         <f t="shared" si="7"/>
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B48" s="118">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
-      <c r="C48" s="48">
+      <c r="C48" s="118">
         <v>3305</v>
       </c>
-      <c r="D48" s="48" t="s">
-        <v>144</v>
+      <c r="D48" s="118" t="s">
+        <v>134</v>
       </c>
       <c r="E48" s="51">
         <v>1.67</v>
       </c>
       <c r="F48" s="52">
-        <v>1121753.42</v>
+        <v>1240769.42</v>
       </c>
       <c r="G48" s="53">
         <v>0</v>
@@ -5636,11 +5618,11 @@
       <c r="H48" s="61"/>
       <c r="I48" s="55">
         <f t="shared" si="2"/>
-        <v>1121753.42</v>
+        <v>1240769.42</v>
       </c>
       <c r="J48" s="55">
         <f t="shared" si="3"/>
-        <v>33091.725890000002</v>
+        <v>36602.697890000003</v>
       </c>
       <c r="K48" s="56">
         <f t="shared" si="4"/>
@@ -5648,44 +5630,44 @@
       </c>
       <c r="L48" s="56">
         <f t="shared" si="5"/>
-        <v>85924.236962999974</v>
+        <v>113226.66065200001</v>
       </c>
       <c r="M48" s="57">
         <v>0</v>
       </c>
       <c r="N48" s="58">
         <f t="shared" si="0"/>
-        <v>1240769.42</v>
+        <v>1390599.42</v>
       </c>
       <c r="O48" s="59">
         <f t="shared" si="1"/>
-        <v>1277992.42</v>
+        <v>1432317.42</v>
       </c>
       <c r="P48" s="37">
         <f t="shared" si="7"/>
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" s="118">
         <f t="shared" si="8"/>
         <v>43</v>
       </c>
-      <c r="C49" s="48">
+      <c r="C49" s="118">
         <v>4406</v>
       </c>
-      <c r="D49" s="48" t="s">
-        <v>145</v>
+      <c r="D49" s="118" t="s">
+        <v>135</v>
       </c>
       <c r="E49" s="51">
         <v>2.17</v>
       </c>
       <c r="F49" s="52">
-        <v>65050.43</v>
+        <v>111650.43</v>
       </c>
       <c r="G49" s="53">
         <f>F49</f>
-        <v>65050.43</v>
+        <v>111650.43</v>
       </c>
       <c r="H49" s="61"/>
       <c r="I49" s="55">
@@ -5702,44 +5684,44 @@
       </c>
       <c r="L49" s="56">
         <f t="shared" si="5"/>
-        <v>111650.05641299997</v>
+        <v>147126.85845200001</v>
       </c>
       <c r="M49" s="57">
         <v>0</v>
       </c>
       <c r="N49" s="58">
         <f t="shared" si="0"/>
-        <v>111650.43</v>
+        <v>147127.43</v>
       </c>
       <c r="O49" s="59">
         <f t="shared" si="1"/>
-        <v>115000.43</v>
+        <v>151541.43</v>
       </c>
       <c r="P49" s="37">
         <f t="shared" si="7"/>
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50" s="118">
         <f t="shared" si="8"/>
         <v>44</v>
       </c>
-      <c r="C50" s="48">
+      <c r="C50" s="118">
         <v>4407</v>
       </c>
-      <c r="D50" s="48" t="s">
-        <v>146</v>
+      <c r="D50" s="118" t="s">
+        <v>136</v>
       </c>
       <c r="E50" s="51">
         <v>1.23</v>
       </c>
       <c r="F50" s="52">
-        <v>44159.44</v>
+        <v>63286.44</v>
       </c>
       <c r="G50" s="53">
         <f>F50</f>
-        <v>44159.44</v>
+        <v>63286.44</v>
       </c>
       <c r="H50" s="61"/>
       <c r="I50" s="55">
@@ -5756,52 +5738,52 @@
       </c>
       <c r="L50" s="56">
         <f t="shared" si="5"/>
-        <v>63285.515846999988</v>
+        <v>83394.486588000014</v>
       </c>
       <c r="M50" s="57">
         <v>0</v>
       </c>
       <c r="N50" s="58">
         <f t="shared" si="0"/>
-        <v>63286.44</v>
+        <v>83394.44</v>
       </c>
       <c r="O50" s="59">
         <f t="shared" si="1"/>
-        <v>65185.440000000002</v>
+        <v>85896.44</v>
       </c>
       <c r="P50" s="37">
         <f t="shared" si="7"/>
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="118">
         <f t="shared" si="8"/>
         <v>45</v>
       </c>
-      <c r="C51" s="48">
+      <c r="C51" s="118">
         <v>4408</v>
       </c>
-      <c r="D51" s="48" t="s">
-        <v>147</v>
+      <c r="D51" s="118" t="s">
+        <v>137</v>
       </c>
       <c r="E51" s="51">
         <v>1.29</v>
       </c>
       <c r="F51" s="52">
-        <v>46313.45</v>
+        <v>114052.45</v>
       </c>
       <c r="G51" s="53">
-        <v>0</v>
+        <v>66373</v>
       </c>
       <c r="H51" s="61"/>
       <c r="I51" s="55">
         <f t="shared" si="2"/>
-        <v>46313.45</v>
+        <v>47679.45</v>
       </c>
       <c r="J51" s="55">
         <f t="shared" si="3"/>
-        <v>1366.2467750000001</v>
+        <v>1406.5437750000001</v>
       </c>
       <c r="K51" s="56">
         <f t="shared" si="4"/>
@@ -5809,52 +5791,52 @@
       </c>
       <c r="L51" s="56">
         <f t="shared" si="5"/>
-        <v>66372.614180999983</v>
+        <v>87462.510324000003</v>
       </c>
       <c r="M51" s="57">
         <v>0</v>
       </c>
       <c r="N51" s="58">
         <f t="shared" si="0"/>
-        <v>114052.45</v>
+        <v>136549.45000000001</v>
       </c>
       <c r="O51" s="59">
         <f t="shared" si="1"/>
-        <v>117474.45</v>
+        <v>140645.45000000001</v>
       </c>
       <c r="P51" s="37">
         <f t="shared" si="7"/>
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B52" s="240">
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B52" s="118">
         <f t="shared" si="8"/>
         <v>46</v>
       </c>
-      <c r="C52" s="240">
+      <c r="C52" s="118">
         <v>4401</v>
       </c>
-      <c r="D52" s="240" t="s">
-        <v>148</v>
+      <c r="D52" s="118" t="s">
+        <v>138</v>
       </c>
       <c r="E52" s="51">
         <v>1.36</v>
       </c>
       <c r="F52" s="52">
-        <v>48826.46</v>
+        <v>72561.460000000006</v>
       </c>
       <c r="G52" s="53">
-        <v>46313.46</v>
+        <v>74738.460000000006</v>
       </c>
       <c r="H52" s="61"/>
       <c r="I52" s="55">
         <f t="shared" si="2"/>
-        <v>2513</v>
+        <v>-2177</v>
       </c>
       <c r="J52" s="55">
         <f t="shared" si="3"/>
-        <v>74.133499999999998</v>
+        <v>0</v>
       </c>
       <c r="K52" s="56">
         <f t="shared" si="4"/>
@@ -5862,48 +5844,48 @@
       </c>
       <c r="L52" s="56">
         <f t="shared" si="5"/>
-        <v>69974.228903999989</v>
+        <v>92208.53801600002</v>
       </c>
       <c r="M52" s="57">
         <v>0</v>
       </c>
       <c r="N52" s="58">
         <f t="shared" si="0"/>
-        <v>72561.460000000006</v>
+        <v>90032.46</v>
       </c>
       <c r="O52" s="59">
         <f t="shared" si="1"/>
-        <v>74738.460000000006</v>
+        <v>92733.46</v>
       </c>
       <c r="P52" s="37">
         <f t="shared" si="7"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B53" s="240">
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B53" s="118">
         <f t="shared" si="8"/>
         <v>47</v>
       </c>
-      <c r="C53" s="240">
+      <c r="C53" s="118">
         <v>4402</v>
       </c>
-      <c r="D53" s="240" t="s">
-        <v>149</v>
+      <c r="D53" s="118" t="s">
+        <v>139</v>
       </c>
       <c r="E53" s="51">
         <v>0.57999999999999996</v>
       </c>
       <c r="F53" s="52">
-        <v>20823.47</v>
+        <v>-20334.53</v>
       </c>
       <c r="G53" s="53">
-        <v>71000</v>
+        <v>20944.53</v>
       </c>
       <c r="H53" s="61"/>
       <c r="I53" s="55">
         <f t="shared" si="2"/>
-        <v>-50176.53</v>
+        <v>-41279.06</v>
       </c>
       <c r="J53" s="55">
         <f t="shared" si="3"/>
@@ -5915,53 +5897,53 @@
       </c>
       <c r="L53" s="56">
         <f t="shared" si="5"/>
-        <v>29841.950561999991</v>
+        <v>39324.229447999998</v>
       </c>
       <c r="M53" s="57">
         <v>0</v>
       </c>
       <c r="N53" s="58">
         <f t="shared" si="0"/>
-        <v>-20334.53</v>
+        <v>-1954.53</v>
       </c>
       <c r="O53" s="59">
         <f t="shared" si="1"/>
-        <v>-20944.53</v>
+        <v>-2013.53</v>
       </c>
       <c r="P53" s="37">
         <f t="shared" si="7"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="118">
         <f t="shared" si="8"/>
         <v>48</v>
       </c>
-      <c r="C54" s="48">
+      <c r="C54" s="118">
         <v>4403</v>
       </c>
-      <c r="D54" s="48" t="s">
-        <v>150</v>
+      <c r="D54" s="118" t="s">
+        <v>140</v>
       </c>
       <c r="E54" s="51">
         <v>0.57999999999999996</v>
       </c>
       <c r="F54" s="52">
-        <v>20823.48</v>
+        <v>29842.48</v>
       </c>
       <c r="G54" s="53">
-        <f>129605-G55-G56</f>
-        <v>20823.010000000009</v>
+        <f>191313.49-G55-G56</f>
+        <v>35414.499999999985</v>
       </c>
       <c r="H54" s="61"/>
       <c r="I54" s="55">
         <f t="shared" si="2"/>
-        <v>0.46999999999025022</v>
+        <v>-5572.0199999999859</v>
       </c>
       <c r="J54" s="55">
         <f t="shared" si="3"/>
-        <v>1.3864999999712382E-2</v>
+        <v>0</v>
       </c>
       <c r="K54" s="56">
         <f t="shared" si="4"/>
@@ -5969,47 +5951,47 @@
       </c>
       <c r="L54" s="56">
         <f t="shared" si="5"/>
-        <v>29841.950561999991</v>
+        <v>39324.229447999998</v>
       </c>
       <c r="M54" s="57">
         <v>0</v>
       </c>
       <c r="N54" s="58">
         <f t="shared" si="0"/>
-        <v>29842.48</v>
+        <v>33752.480000000003</v>
       </c>
       <c r="O54" s="59">
         <f t="shared" si="1"/>
-        <v>30737.48</v>
+        <v>34765.480000000003</v>
       </c>
       <c r="P54" s="37">
         <f t="shared" si="7"/>
         <v>0.48000000000000026</v>
       </c>
       <c r="Q54" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="118">
         <f t="shared" si="8"/>
         <v>49</v>
       </c>
-      <c r="C55" s="48">
+      <c r="C55" s="118">
         <v>4404</v>
       </c>
-      <c r="D55" s="48" t="s">
-        <v>150</v>
+      <c r="D55" s="118" t="s">
+        <v>140</v>
       </c>
       <c r="E55" s="51">
         <v>1.36</v>
       </c>
       <c r="F55" s="52">
-        <v>48826.49</v>
+        <v>69974.490000000005</v>
       </c>
       <c r="G55" s="53">
         <f>F55</f>
-        <v>48826.49</v>
+        <v>69974.490000000005</v>
       </c>
       <c r="H55" s="61"/>
       <c r="I55" s="55">
@@ -6026,47 +6008,47 @@
       </c>
       <c r="L55" s="56">
         <f t="shared" si="5"/>
-        <v>69974.228903999989</v>
+        <v>92208.53801600002</v>
       </c>
       <c r="M55" s="57">
         <v>0</v>
       </c>
       <c r="N55" s="58">
         <f t="shared" si="0"/>
-        <v>69974.490000000005</v>
+        <v>92209.49</v>
       </c>
       <c r="O55" s="59">
         <f t="shared" si="1"/>
-        <v>72073.490000000005</v>
+        <v>94975.49</v>
       </c>
       <c r="P55" s="37">
         <f t="shared" si="7"/>
         <v>0.49000000000000027</v>
       </c>
       <c r="Q55" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="118">
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="C56" s="48">
+      <c r="C56" s="118">
         <v>4405</v>
       </c>
-      <c r="D56" s="48" t="s">
-        <v>150</v>
+      <c r="D56" s="118" t="s">
+        <v>140</v>
       </c>
       <c r="E56" s="51">
         <v>1.67</v>
       </c>
       <c r="F56" s="52">
-        <v>59955.5</v>
+        <v>85924.5</v>
       </c>
       <c r="G56" s="53">
         <f>F56</f>
-        <v>59955.5</v>
+        <v>85924.5</v>
       </c>
       <c r="H56" s="61"/>
       <c r="I56" s="55">
@@ -6083,52 +6065,51 @@
       </c>
       <c r="L56" s="56">
         <f t="shared" si="5"/>
-        <v>85924.236962999974</v>
+        <v>113226.66065200001</v>
       </c>
       <c r="M56" s="57">
         <v>0</v>
       </c>
       <c r="N56" s="58">
         <f t="shared" si="0"/>
-        <v>85924.5</v>
+        <v>113227.5</v>
       </c>
       <c r="O56" s="59">
         <f t="shared" si="1"/>
-        <v>88502.5</v>
+        <v>116624.5</v>
       </c>
       <c r="P56" s="37">
         <f t="shared" si="7"/>
         <v>0.50000000000000022</v>
       </c>
       <c r="Q56" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="118">
         <f t="shared" si="8"/>
         <v>51</v>
       </c>
-      <c r="C57" s="48">
+      <c r="C57" s="118">
         <v>5506</v>
       </c>
-      <c r="D57" s="48" t="s">
-        <v>151</v>
+      <c r="D57" s="118" t="s">
+        <v>141</v>
       </c>
       <c r="E57" s="51">
         <v>2.17</v>
       </c>
       <c r="F57" s="52">
-        <v>77906.509999999995</v>
+        <v>111650.51</v>
       </c>
       <c r="G57" s="53">
-        <f>F57</f>
-        <v>77906.509999999995</v>
+        <v>115000.51</v>
       </c>
       <c r="H57" s="61"/>
       <c r="I57" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-3350</v>
       </c>
       <c r="J57" s="55">
         <f t="shared" si="3"/>
@@ -6140,40 +6121,40 @@
       </c>
       <c r="L57" s="56">
         <f t="shared" si="5"/>
-        <v>111650.05641299997</v>
+        <v>147126.85845200001</v>
       </c>
       <c r="M57" s="57">
         <v>0</v>
       </c>
       <c r="N57" s="58">
         <f t="shared" si="0"/>
-        <v>111650.51</v>
+        <v>143777.51</v>
       </c>
       <c r="O57" s="59">
         <f t="shared" si="1"/>
-        <v>115000.51</v>
+        <v>148090.51</v>
       </c>
       <c r="P57" s="37">
         <f t="shared" si="7"/>
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B58" s="118">
         <f t="shared" si="8"/>
         <v>52</v>
       </c>
-      <c r="C58" s="48">
+      <c r="C58" s="118">
         <v>5507</v>
       </c>
-      <c r="D58" s="48" t="s">
-        <v>152</v>
+      <c r="D58" s="118" t="s">
+        <v>142</v>
       </c>
       <c r="E58" s="51">
         <v>1.79</v>
       </c>
       <c r="F58" s="52">
-        <v>64263.519999999997</v>
+        <v>158258.51999999999</v>
       </c>
       <c r="G58" s="53">
         <v>0</v>
@@ -6181,11 +6162,11 @@
       <c r="H58" s="61"/>
       <c r="I58" s="55">
         <f t="shared" si="2"/>
-        <v>64263.519999999997</v>
+        <v>158258.51999999999</v>
       </c>
       <c r="J58" s="55">
         <f t="shared" si="3"/>
-        <v>1895.7738400000001</v>
+        <v>4668.6263399999998</v>
       </c>
       <c r="K58" s="56">
         <f t="shared" si="4"/>
@@ -6193,40 +6174,40 @@
       </c>
       <c r="L58" s="56">
         <f t="shared" si="5"/>
-        <v>92098.433630999978</v>
+        <v>121362.708124</v>
       </c>
       <c r="M58" s="57">
         <v>0</v>
       </c>
       <c r="N58" s="58">
         <f t="shared" si="0"/>
-        <v>158258.51999999999</v>
+        <v>284290.52</v>
       </c>
       <c r="O58" s="59">
         <f t="shared" si="1"/>
-        <v>163006.51999999999</v>
+        <v>292819.52</v>
       </c>
       <c r="P58" s="37">
         <f t="shared" si="7"/>
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="118">
         <f t="shared" si="8"/>
         <v>53</v>
       </c>
-      <c r="C59" s="48">
+      <c r="C59" s="118">
         <v>5508</v>
       </c>
-      <c r="D59" s="48" t="s">
-        <v>153</v>
+      <c r="D59" s="118" t="s">
+        <v>143</v>
       </c>
       <c r="E59" s="51">
         <v>1.29</v>
       </c>
       <c r="F59" s="52">
-        <v>-236875.7</v>
+        <v>-170502.47</v>
       </c>
       <c r="G59" s="53">
         <v>0</v>
@@ -6234,7 +6215,7 @@
       <c r="H59" s="61"/>
       <c r="I59" s="55">
         <f t="shared" si="2"/>
-        <v>-236875.7</v>
+        <v>-170502.47</v>
       </c>
       <c r="J59" s="55">
         <f t="shared" si="3"/>
@@ -6246,52 +6227,52 @@
       </c>
       <c r="L59" s="56">
         <f t="shared" si="5"/>
-        <v>66372.614180999983</v>
+        <v>87462.510324000003</v>
       </c>
       <c r="M59" s="57">
         <v>0</v>
       </c>
       <c r="N59" s="58">
         <f t="shared" si="0"/>
-        <v>-170502.47</v>
+        <v>-83039.47</v>
       </c>
       <c r="O59" s="59">
         <f t="shared" si="1"/>
-        <v>-175617.47</v>
+        <v>-85530.47</v>
       </c>
       <c r="P59" s="37">
         <f t="shared" si="7"/>
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" s="118">
         <f t="shared" si="8"/>
         <v>54</v>
       </c>
-      <c r="C60" s="48">
+      <c r="C60" s="118">
         <v>5501</v>
       </c>
-      <c r="D60" s="48" t="s">
-        <v>154</v>
+      <c r="D60" s="118" t="s">
+        <v>144</v>
       </c>
       <c r="E60" s="51">
         <v>1.36</v>
       </c>
       <c r="F60" s="52">
-        <v>48579.54</v>
+        <v>119987.54</v>
       </c>
       <c r="G60" s="53">
-        <v>0</v>
+        <v>123587.54</v>
       </c>
       <c r="H60" s="61"/>
       <c r="I60" s="55">
         <f t="shared" si="2"/>
-        <v>48579.54</v>
+        <v>-3600</v>
       </c>
       <c r="J60" s="55">
         <f t="shared" si="3"/>
-        <v>1433.0964300000001</v>
+        <v>0</v>
       </c>
       <c r="K60" s="56">
         <f t="shared" si="4"/>
@@ -6299,52 +6280,52 @@
       </c>
       <c r="L60" s="56">
         <f t="shared" si="5"/>
-        <v>69974.228903999989</v>
+        <v>92208.53801600002</v>
       </c>
       <c r="M60" s="57">
         <v>0</v>
       </c>
       <c r="N60" s="58">
         <f t="shared" si="0"/>
-        <v>119987.54</v>
+        <v>88609.54</v>
       </c>
       <c r="O60" s="59">
         <f t="shared" si="1"/>
-        <v>123587.54</v>
+        <v>91267.54</v>
       </c>
       <c r="P60" s="37">
         <f t="shared" si="7"/>
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" s="118">
         <f t="shared" si="8"/>
         <v>55</v>
       </c>
-      <c r="C61" s="48">
+      <c r="C61" s="118">
         <v>5503</v>
       </c>
-      <c r="D61" s="48" t="s">
-        <v>155</v>
+      <c r="D61" s="118" t="s">
+        <v>145</v>
       </c>
       <c r="E61" s="51">
         <v>0.57999999999999996</v>
       </c>
       <c r="F61" s="52">
-        <v>974029.55</v>
+        <v>1032605.55</v>
       </c>
       <c r="G61" s="53">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="H61" s="61"/>
       <c r="I61" s="55">
         <f t="shared" si="2"/>
-        <v>974029.55</v>
+        <v>732605.55</v>
       </c>
       <c r="J61" s="55">
         <f t="shared" si="3"/>
-        <v>28733.871725000005</v>
+        <v>21611.863725000003</v>
       </c>
       <c r="K61" s="56">
         <f t="shared" si="4"/>
@@ -6352,49 +6333,51 @@
       </c>
       <c r="L61" s="56">
         <f t="shared" si="5"/>
-        <v>29841.950561999991</v>
+        <v>39324.229447999998</v>
       </c>
       <c r="M61" s="57">
         <v>0</v>
       </c>
       <c r="N61" s="58">
         <f t="shared" si="0"/>
-        <v>1032605.55</v>
+        <v>793542.55</v>
       </c>
       <c r="O61" s="59">
         <f t="shared" si="1"/>
-        <v>1063583.55</v>
+        <v>817348.55</v>
       </c>
       <c r="P61" s="37">
         <f t="shared" si="7"/>
         <v>0.55000000000000027</v>
       </c>
-    </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="Q61" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" s="118">
         <f t="shared" si="8"/>
         <v>56</v>
       </c>
-      <c r="C62" s="48">
+      <c r="C62" s="118">
         <v>5504</v>
       </c>
-      <c r="D62" s="48" t="s">
-        <v>84</v>
+      <c r="D62" s="118" t="s">
+        <v>83</v>
       </c>
       <c r="E62" s="51">
         <v>1.36</v>
       </c>
       <c r="F62" s="52">
-        <v>48810.559999999998</v>
+        <v>68785.56</v>
       </c>
       <c r="G62" s="53">
-        <f>50000</f>
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="H62" s="61"/>
       <c r="I62" s="55">
         <f t="shared" si="2"/>
-        <v>-1189.4400000000023</v>
+        <v>-1214.4400000000023</v>
       </c>
       <c r="J62" s="55">
         <f t="shared" si="3"/>
@@ -6406,40 +6389,40 @@
       </c>
       <c r="L62" s="56">
         <f t="shared" si="5"/>
-        <v>69974.228903999989</v>
+        <v>92208.53801600002</v>
       </c>
       <c r="M62" s="57">
         <v>0</v>
       </c>
       <c r="N62" s="58">
         <f t="shared" si="0"/>
-        <v>68785.56</v>
+        <v>90994.559999999998</v>
       </c>
       <c r="O62" s="59">
         <f t="shared" si="1"/>
-        <v>70849.56</v>
+        <v>93724.56</v>
       </c>
       <c r="P62" s="37">
         <f t="shared" si="7"/>
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="118">
         <f t="shared" si="8"/>
         <v>57</v>
       </c>
-      <c r="C63" s="48">
+      <c r="C63" s="118">
         <v>5502</v>
       </c>
-      <c r="D63" s="48" t="s">
-        <v>80</v>
+      <c r="D63" s="118" t="s">
+        <v>79</v>
       </c>
       <c r="E63" s="51">
         <v>0.57999999999999996</v>
       </c>
       <c r="F63" s="52">
-        <v>20822.57</v>
+        <v>51279.57</v>
       </c>
       <c r="G63" s="53">
         <v>0</v>
@@ -6447,11 +6430,11 @@
       <c r="H63" s="61"/>
       <c r="I63" s="55">
         <f t="shared" si="2"/>
-        <v>20822.57</v>
+        <v>51279.57</v>
       </c>
       <c r="J63" s="55">
         <f t="shared" si="3"/>
-        <v>614.26581499999998</v>
+        <v>1512.7473150000001</v>
       </c>
       <c r="K63" s="56">
         <f t="shared" si="4"/>
@@ -6459,52 +6442,52 @@
       </c>
       <c r="L63" s="56">
         <f t="shared" si="5"/>
-        <v>29841.950561999991</v>
+        <v>39324.229447999998</v>
       </c>
       <c r="M63" s="57">
         <v>0</v>
       </c>
       <c r="N63" s="58">
         <f t="shared" si="0"/>
-        <v>51279.57</v>
+        <v>92117.57</v>
       </c>
       <c r="O63" s="59">
         <f t="shared" si="1"/>
-        <v>52817.57</v>
+        <v>94881.57</v>
       </c>
       <c r="P63" s="37">
         <f t="shared" si="7"/>
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" s="118">
         <f t="shared" si="8"/>
         <v>58</v>
       </c>
-      <c r="C64" s="48">
+      <c r="C64" s="118">
         <v>5505</v>
       </c>
-      <c r="D64" s="48" t="s">
-        <v>156</v>
+      <c r="D64" s="118" t="s">
+        <v>146</v>
       </c>
       <c r="E64" s="51">
         <v>1.67</v>
       </c>
       <c r="F64" s="52">
-        <v>175844.58</v>
+        <v>149987.57999999999</v>
       </c>
       <c r="G64" s="53">
-        <v>113617.58</v>
+        <v>149987.57999999999</v>
       </c>
       <c r="H64" s="61"/>
       <c r="I64" s="55">
         <f t="shared" si="2"/>
-        <v>62226.999999999985</v>
+        <v>0</v>
       </c>
       <c r="J64" s="55">
         <f t="shared" si="3"/>
-        <v>1835.6964999999998</v>
+        <v>0</v>
       </c>
       <c r="K64" s="56">
         <f t="shared" si="4"/>
@@ -6512,25 +6495,25 @@
       </c>
       <c r="L64" s="56">
         <f t="shared" si="5"/>
-        <v>85924.236962999974</v>
+        <v>113226.66065200001</v>
       </c>
       <c r="M64" s="57">
         <v>0</v>
       </c>
       <c r="N64" s="58">
         <f t="shared" si="0"/>
-        <v>149987.57999999999</v>
+        <v>113227.58</v>
       </c>
       <c r="O64" s="59">
         <f t="shared" si="1"/>
-        <v>154487.57999999999</v>
+        <v>116624.58</v>
       </c>
       <c r="P64" s="37">
         <f t="shared" si="7"/>
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B65" s="118"/>
       <c r="C65" s="48"/>
       <c r="D65" s="48"/>
@@ -6547,21 +6530,21 @@
       <c r="O65" s="52"/>
       <c r="P65" s="37"/>
     </row>
-    <row r="66" spans="2:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="64"/>
       <c r="C66" s="65"/>
       <c r="D66" s="136"/>
-      <c r="E66" s="139">
+      <c r="E66" s="138">
         <f>SUM(E6:E64)</f>
         <v>99.940000000000026</v>
       </c>
       <c r="F66" s="66">
         <f>SUM(F6:F64)</f>
-        <v>22483257.809999999</v>
+        <v>25420650.140000001</v>
       </c>
       <c r="G66" s="66">
         <f>SUM(G6:G64)</f>
-        <v>2804769.5600000005</v>
+        <v>4171978.8499999996</v>
       </c>
       <c r="H66" s="137">
         <f t="shared" ref="H66" si="9">SUM(H6:H45)</f>
@@ -6569,11 +6552,11 @@
       </c>
       <c r="I66" s="66">
         <f t="shared" ref="I66:O66" si="10">SUM(I6:I64)</f>
-        <v>19678488.249999996</v>
+        <v>21248671.290000007</v>
       </c>
       <c r="J66" s="66">
         <f t="shared" si="10"/>
-        <v>590895.35568000004</v>
+        <v>635871.87076500012</v>
       </c>
       <c r="K66" s="66">
         <f t="shared" si="10"/>
@@ -6581,7 +6564,7 @@
       </c>
       <c r="L66" s="66">
         <f t="shared" si="10"/>
-        <v>5142076.7916659964</v>
+        <v>6775971.5362640023</v>
       </c>
       <c r="M66" s="66">
         <f t="shared" si="10"/>
@@ -6589,18 +6572,18 @@
       </c>
       <c r="N66" s="66">
         <f t="shared" si="10"/>
-        <v>25411480.109999999</v>
+        <v>28660539.109999999</v>
       </c>
       <c r="O66" s="66">
         <f t="shared" si="10"/>
-        <v>26173832.109999999</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>29520353.109999999</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="41"/>
     </row>
-    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="204" t="s">
         <v>70</v>
       </c>
@@ -6615,7 +6598,7 @@
       <c r="M69" s="204"/>
       <c r="N69" s="204"/>
     </row>
-    <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="204"/>
       <c r="E70" s="204"/>
       <c r="F70" s="204"/>
@@ -6628,7 +6611,7 @@
       <c r="M70" s="204"/>
       <c r="N70" s="204"/>
     </row>
-    <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="204"/>
       <c r="E71" s="204"/>
       <c r="F71" s="204"/>
@@ -6641,7 +6624,7 @@
       <c r="M71" s="204"/>
       <c r="N71" s="204"/>
     </row>
-    <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="204"/>
       <c r="E72" s="204"/>
       <c r="F72" s="204"/>
@@ -6654,7 +6637,7 @@
       <c r="M72" s="204"/>
       <c r="N72" s="204"/>
     </row>
-    <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="204"/>
       <c r="E73" s="204"/>
       <c r="F73" s="204"/>
@@ -6667,7 +6650,7 @@
       <c r="M73" s="204"/>
       <c r="N73" s="204"/>
     </row>
-    <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="204"/>
       <c r="E74" s="204"/>
       <c r="F74" s="204"/>
@@ -6682,11 +6665,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D69:N74"/>
@@ -6699,6 +6677,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B3:O3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6707,339 +6690,393 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
-  <dimension ref="C2:H48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="C2:K48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C3" s="153" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="154">
+    <row r="2" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="151" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="152">
         <v>1</v>
       </c>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="151"/>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C4" s="155" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="156" t="s">
-        <v>193</v>
-      </c>
-      <c r="H4" s="152"/>
-    </row>
-    <row r="5" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="155"/>
-      <c r="D5" s="156"/>
-      <c r="H5" s="152"/>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="231" t="s">
-        <v>196</v>
-      </c>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="232"/>
-      <c r="G6" s="232"/>
-      <c r="H6" s="233"/>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="234"/>
-      <c r="D7" s="235"/>
-      <c r="E7" s="235"/>
-      <c r="F7" s="235"/>
-      <c r="G7" s="235"/>
-      <c r="H7" s="236"/>
-    </row>
-    <row r="8" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="237"/>
-      <c r="D8" s="238"/>
-      <c r="E8" s="238"/>
-      <c r="F8" s="238"/>
-      <c r="G8" s="238"/>
-      <c r="H8" s="239"/>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="148"/>
+      <c r="H3" s="149"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C4" s="153" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="154" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" s="150"/>
+    </row>
+    <row r="5" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="153"/>
+      <c r="D5" s="154"/>
+      <c r="H5" s="150"/>
+      <c r="I5" s="162"/>
+      <c r="J5" s="162"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C6" s="216" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="218"/>
+      <c r="I6" s="162"/>
+      <c r="J6" s="162"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C7" s="219"/>
+      <c r="D7" s="220"/>
+      <c r="E7" s="220"/>
+      <c r="F7" s="220"/>
+      <c r="G7" s="220"/>
+      <c r="H7" s="221"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="162"/>
+    </row>
+    <row r="8" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="222"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="224"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" s="104"/>
       <c r="D9" s="104"/>
       <c r="E9" s="104"/>
     </row>
-    <row r="10" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="104"/>
       <c r="D10" s="104"/>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C11" s="159" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="160">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C11" s="156" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="157">
         <f>D3+1</f>
         <v>2</v>
       </c>
-      <c r="E11" s="150"/>
-      <c r="F11" s="150"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="151"/>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="161" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="158">
+      <c r="E11" s="148"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="148"/>
+      <c r="H11" s="149"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C12" s="158" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="155">
         <v>41</v>
       </c>
-      <c r="H12" s="152"/>
-    </row>
-    <row r="13" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="161"/>
-      <c r="D13" s="158"/>
-      <c r="H13" s="152"/>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="231" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="232"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="232"/>
-      <c r="G14" s="232"/>
-      <c r="H14" s="233"/>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C15" s="234"/>
-      <c r="D15" s="235"/>
-      <c r="E15" s="235"/>
-      <c r="F15" s="235"/>
-      <c r="G15" s="235"/>
-      <c r="H15" s="236"/>
-    </row>
-    <row r="16" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="237"/>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="238"/>
-      <c r="G16" s="238"/>
-      <c r="H16" s="239"/>
-    </row>
-    <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C19" s="162" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" s="163">
+      <c r="H12" s="150"/>
+    </row>
+    <row r="13" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="158"/>
+      <c r="D13" s="155"/>
+      <c r="H13" s="150"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="162"/>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C14" s="216" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="217"/>
+      <c r="E14" s="217"/>
+      <c r="F14" s="217"/>
+      <c r="G14" s="217"/>
+      <c r="H14" s="218"/>
+      <c r="I14" s="162"/>
+      <c r="J14" s="162"/>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C15" s="219"/>
+      <c r="D15" s="220"/>
+      <c r="E15" s="220"/>
+      <c r="F15" s="220"/>
+      <c r="G15" s="220"/>
+      <c r="H15" s="221"/>
+    </row>
+    <row r="16" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="222"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
+      <c r="F16" s="223"/>
+      <c r="G16" s="223"/>
+      <c r="H16" s="224"/>
+    </row>
+    <row r="18" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C19" s="159" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="160">
         <f>D11+1</f>
         <v>3</v>
       </c>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="151"/>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C20" s="164" t="s">
-        <v>174</v>
-      </c>
-      <c r="D20" s="165" t="s">
-        <v>175</v>
-      </c>
-      <c r="H20" s="152"/>
-    </row>
-    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="164"/>
-      <c r="D21" s="165"/>
-      <c r="H21" s="152"/>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="222" t="s">
-        <v>176</v>
-      </c>
-      <c r="D22" s="223"/>
-      <c r="E22" s="223"/>
-      <c r="F22" s="223"/>
-      <c r="G22" s="223"/>
-      <c r="H22" s="224"/>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="225"/>
-      <c r="D23" s="226"/>
-      <c r="E23" s="226"/>
-      <c r="F23" s="226"/>
-      <c r="G23" s="226"/>
-      <c r="H23" s="227"/>
-    </row>
-    <row r="24" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="228"/>
-      <c r="D24" s="229"/>
-      <c r="E24" s="229"/>
-      <c r="F24" s="229"/>
-      <c r="G24" s="229"/>
-      <c r="H24" s="230"/>
-    </row>
-    <row r="26" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C27" s="172" t="s">
-        <v>173</v>
-      </c>
-      <c r="D27" s="173">
+      <c r="E19" s="148"/>
+      <c r="F19" s="148"/>
+      <c r="G19" s="148"/>
+      <c r="H19" s="149"/>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C20" s="161" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>158</v>
+      </c>
+      <c r="H20" s="150"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="162"/>
+      <c r="K20" s="162"/>
+    </row>
+    <row r="21" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="161"/>
+      <c r="D21" s="162"/>
+      <c r="H21" s="150"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="162"/>
+      <c r="K21" s="162"/>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C22" s="216" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="217"/>
+      <c r="E22" s="217"/>
+      <c r="F22" s="217"/>
+      <c r="G22" s="217"/>
+      <c r="H22" s="218"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="162"/>
+      <c r="K22" s="162"/>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C23" s="219"/>
+      <c r="D23" s="220"/>
+      <c r="E23" s="220"/>
+      <c r="F23" s="220"/>
+      <c r="G23" s="220"/>
+      <c r="H23" s="221"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="162"/>
+      <c r="K23" s="162"/>
+    </row>
+    <row r="24" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="222"/>
+      <c r="D24" s="223"/>
+      <c r="E24" s="223"/>
+      <c r="F24" s="223"/>
+      <c r="G24" s="223"/>
+      <c r="H24" s="224"/>
+    </row>
+    <row r="26" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="166" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="167">
         <f>D19+1</f>
         <v>4</v>
       </c>
-      <c r="E27" s="150"/>
-      <c r="F27" s="150"/>
-      <c r="G27" s="150"/>
-      <c r="H27" s="151"/>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C28" s="174" t="s">
+      <c r="E27" s="148"/>
+      <c r="F27" s="148"/>
+      <c r="G27" s="148"/>
+      <c r="H27" s="149"/>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C28" s="168" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" s="169" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" s="150"/>
+    </row>
+    <row r="29" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="168"/>
+      <c r="D29" s="169"/>
+      <c r="H29" s="150"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="162"/>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C30" s="216" t="s">
         <v>174</v>
       </c>
-      <c r="D28" s="175" t="s">
-        <v>191</v>
-      </c>
-      <c r="H28" s="152"/>
-    </row>
-    <row r="29" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C29" s="174"/>
-      <c r="D29" s="175"/>
-      <c r="H29" s="152"/>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C30" s="222" t="s">
-        <v>192</v>
-      </c>
-      <c r="D30" s="223"/>
-      <c r="E30" s="223"/>
-      <c r="F30" s="223"/>
-      <c r="G30" s="223"/>
-      <c r="H30" s="224"/>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C31" s="225"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="226"/>
-      <c r="H31" s="227"/>
-    </row>
-    <row r="32" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="228"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="230"/>
-    </row>
-    <row r="34" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C35" s="177" t="s">
-        <v>173</v>
-      </c>
-      <c r="D35" s="178">
+      <c r="D30" s="217"/>
+      <c r="E30" s="217"/>
+      <c r="F30" s="217"/>
+      <c r="G30" s="217"/>
+      <c r="H30" s="218"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="162"/>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C31" s="219"/>
+      <c r="D31" s="220"/>
+      <c r="E31" s="220"/>
+      <c r="F31" s="220"/>
+      <c r="G31" s="220"/>
+      <c r="H31" s="221"/>
+      <c r="I31" s="162"/>
+      <c r="J31" s="162"/>
+    </row>
+    <row r="32" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="222"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="224"/>
+    </row>
+    <row r="34" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C35" s="170" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="171">
         <f>D27+1</f>
         <v>5</v>
       </c>
-      <c r="E35" s="150"/>
-      <c r="F35" s="150"/>
-      <c r="G35" s="150"/>
-      <c r="H35" s="151"/>
-    </row>
-    <row r="36" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C36" s="179" t="s">
-        <v>174</v>
-      </c>
-      <c r="D36" s="180" t="s">
-        <v>195</v>
-      </c>
-      <c r="H36" s="152"/>
-    </row>
-    <row r="37" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="179"/>
-      <c r="D37" s="180"/>
-      <c r="H37" s="152"/>
-    </row>
-    <row r="38" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C38" s="222" t="s">
-        <v>194</v>
-      </c>
-      <c r="D38" s="223"/>
-      <c r="E38" s="223"/>
-      <c r="F38" s="223"/>
-      <c r="G38" s="223"/>
-      <c r="H38" s="224"/>
-    </row>
-    <row r="39" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C39" s="225"/>
-      <c r="D39" s="226"/>
-      <c r="E39" s="226"/>
-      <c r="F39" s="226"/>
-      <c r="G39" s="226"/>
-      <c r="H39" s="227"/>
-    </row>
-    <row r="40" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="228"/>
-      <c r="D40" s="229"/>
-      <c r="E40" s="229"/>
-      <c r="F40" s="229"/>
-      <c r="G40" s="229"/>
-      <c r="H40" s="230"/>
-    </row>
-    <row r="42" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C43" s="241" t="s">
-        <v>173</v>
-      </c>
-      <c r="D43" s="242">
+      <c r="E35" s="148"/>
+      <c r="F35" s="148"/>
+      <c r="G35" s="148"/>
+      <c r="H35" s="149"/>
+    </row>
+    <row r="36" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C36" s="172" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="173" t="s">
+        <v>177</v>
+      </c>
+      <c r="H36" s="150"/>
+      <c r="I36" s="162"/>
+      <c r="J36" s="162"/>
+    </row>
+    <row r="37" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="172"/>
+      <c r="D37" s="173"/>
+      <c r="H37" s="150"/>
+      <c r="I37" s="162"/>
+      <c r="J37" s="162"/>
+    </row>
+    <row r="38" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C38" s="216" t="s">
+        <v>176</v>
+      </c>
+      <c r="D38" s="217"/>
+      <c r="E38" s="217"/>
+      <c r="F38" s="217"/>
+      <c r="G38" s="217"/>
+      <c r="H38" s="218"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="162"/>
+    </row>
+    <row r="39" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C39" s="219"/>
+      <c r="D39" s="220"/>
+      <c r="E39" s="220"/>
+      <c r="F39" s="220"/>
+      <c r="G39" s="220"/>
+      <c r="H39" s="221"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="162"/>
+    </row>
+    <row r="40" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="222"/>
+      <c r="D40" s="223"/>
+      <c r="E40" s="223"/>
+      <c r="F40" s="223"/>
+      <c r="G40" s="223"/>
+      <c r="H40" s="224"/>
+    </row>
+    <row r="42" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C43" s="174" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="175">
         <f>D35+1</f>
         <v>6</v>
       </c>
-      <c r="E43" s="150"/>
-      <c r="F43" s="150"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="151"/>
-    </row>
-    <row r="44" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C44" s="243" t="s">
-        <v>174</v>
-      </c>
-      <c r="D44" s="244" t="s">
-        <v>197</v>
-      </c>
-      <c r="H44" s="152"/>
-    </row>
-    <row r="45" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C45" s="243"/>
-      <c r="D45" s="244"/>
-      <c r="H45" s="152"/>
-    </row>
-    <row r="46" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C46" s="222" t="s">
-        <v>198</v>
-      </c>
-      <c r="D46" s="223"/>
-      <c r="E46" s="223"/>
-      <c r="F46" s="223"/>
-      <c r="G46" s="223"/>
-      <c r="H46" s="224"/>
-    </row>
-    <row r="47" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C47" s="225"/>
-      <c r="D47" s="226"/>
-      <c r="E47" s="226"/>
-      <c r="F47" s="226"/>
-      <c r="G47" s="226"/>
-      <c r="H47" s="227"/>
-    </row>
-    <row r="48" spans="3:8" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="228"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="230"/>
+      <c r="E43" s="148"/>
+      <c r="F43" s="148"/>
+      <c r="G43" s="148"/>
+      <c r="H43" s="149"/>
+    </row>
+    <row r="44" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C44" s="176" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" s="177" t="s">
+        <v>179</v>
+      </c>
+      <c r="H44" s="150"/>
+      <c r="I44" s="162"/>
+      <c r="J44" s="162"/>
+      <c r="K44" s="162"/>
+    </row>
+    <row r="45" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="176"/>
+      <c r="D45" s="177"/>
+      <c r="H45" s="150"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="162">
+        <f>91683+4000</f>
+        <v>95683</v>
+      </c>
+      <c r="K45" s="162"/>
+    </row>
+    <row r="46" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C46" s="216" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="217"/>
+      <c r="E46" s="217"/>
+      <c r="F46" s="217"/>
+      <c r="G46" s="217"/>
+      <c r="H46" s="218"/>
+      <c r="I46" s="162"/>
+      <c r="J46" s="162"/>
+      <c r="K46" s="162"/>
+    </row>
+    <row r="47" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C47" s="219"/>
+      <c r="D47" s="220"/>
+      <c r="E47" s="220"/>
+      <c r="F47" s="220"/>
+      <c r="G47" s="220"/>
+      <c r="H47" s="221"/>
+      <c r="I47" s="162"/>
+      <c r="J47" s="162"/>
+      <c r="K47" s="162"/>
+    </row>
+    <row r="48" spans="3:11" ht="43.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="222"/>
+      <c r="D48" s="223"/>
+      <c r="E48" s="223"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="223"/>
+      <c r="H48" s="224"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="162"/>
+      <c r="K48" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/2026/GALERIA MITRE/Mayo/Mayo MITRE.xlsx
+++ b/2026/GALERIA MITRE/Mayo/Mayo MITRE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C3206A-73D7-4EC0-B86E-6B23BF1734A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B9ADB5-39FA-472E-BE4D-5A0C6CA80354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1526,40 +1526,112 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1574,72 +1646,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1666,12 +1672,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2100,68 +2100,68 @@
       <c r="D3" s="98"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="180" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="186"/>
+      <c r="B4" s="180"/>
       <c r="C4" s="99"/>
       <c r="D4" s="99"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="186"/>
-      <c r="B5" s="186"/>
+      <c r="A5" s="180"/>
+      <c r="B5" s="180"/>
       <c r="C5" s="99"/>
       <c r="D5" s="99"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="186"/>
-      <c r="B6" s="186"/>
+      <c r="A6" s="180"/>
+      <c r="B6" s="180"/>
       <c r="C6" s="99"/>
       <c r="D6" s="99"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="186"/>
-      <c r="B7" s="186"/>
+      <c r="A7" s="180"/>
+      <c r="B7" s="180"/>
       <c r="C7" s="99"/>
       <c r="D7" s="99"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="181" t="s">
+      <c r="B9" s="191" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="181"/>
+      <c r="B10" s="191"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="181"/>
+      <c r="B11" s="191"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="186" t="s">
+      <c r="A14" s="180" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="186"/>
-      <c r="C14" s="186"/>
-      <c r="D14" s="186"/>
+      <c r="B14" s="180"/>
+      <c r="C14" s="180"/>
+      <c r="D14" s="180"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="186"/>
-      <c r="B15" s="186"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="186"/>
+      <c r="A15" s="180"/>
+      <c r="B15" s="180"/>
+      <c r="C15" s="180"/>
+      <c r="D15" s="180"/>
     </row>
     <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="186"/>
-      <c r="B16" s="186"/>
-      <c r="C16" s="186"/>
-      <c r="D16" s="186"/>
+      <c r="A16" s="180"/>
+      <c r="B16" s="180"/>
+      <c r="C16" s="180"/>
+      <c r="D16" s="180"/>
     </row>
     <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="186"/>
-      <c r="B17" s="186"/>
-      <c r="C17" s="186"/>
-      <c r="D17" s="186"/>
+      <c r="A17" s="180"/>
+      <c r="B17" s="180"/>
+      <c r="C17" s="180"/>
+      <c r="D17" s="180"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2185,10 +2185,10 @@
       <c r="D22" s="23"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="179" t="s">
+      <c r="A23" s="188" t="s">
         <v>193</v>
       </c>
-      <c r="B23" s="180"/>
+      <c r="B23" s="189"/>
       <c r="C23" s="113">
         <v>939981.1</v>
       </c>
@@ -2227,10 +2227,10 @@
       <c r="D26" s="43"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="179" t="s">
+      <c r="A27" s="188" t="s">
         <v>194</v>
       </c>
-      <c r="B27" s="180"/>
+      <c r="B27" s="189"/>
       <c r="C27" s="113">
         <v>849606.52</v>
       </c>
@@ -2372,10 +2372,10 @@
       <c r="D40" s="49"/>
     </row>
     <row r="41" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="182" t="s">
+      <c r="A41" s="184" t="s">
         <v>132</v>
       </c>
-      <c r="B41" s="183"/>
+      <c r="B41" s="185"/>
       <c r="C41" s="127">
         <v>111379</v>
       </c>
@@ -2414,10 +2414,10 @@
       <c r="F44" s="104"/>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="182" t="s">
+      <c r="A45" s="184" t="s">
         <v>183</v>
       </c>
-      <c r="B45" s="183"/>
+      <c r="B45" s="185"/>
       <c r="C45" s="131">
         <v>11596.99</v>
       </c>
@@ -2427,10 +2427,10 @@
       <c r="F45" s="104"/>
     </row>
     <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="182" t="s">
+      <c r="A46" s="184" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="183"/>
+      <c r="B46" s="185"/>
       <c r="C46" s="131">
         <v>11930.96</v>
       </c>
@@ -2578,10 +2578,10 @@
       <c r="D58" s="76"/>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="184" t="s">
+      <c r="A59" s="186" t="s">
         <v>164</v>
       </c>
-      <c r="B59" s="185"/>
+      <c r="B59" s="187"/>
       <c r="C59" s="116">
         <v>171600</v>
       </c>
@@ -2590,10 +2590,10 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="184" t="s">
+      <c r="A60" s="186" t="s">
         <v>166</v>
       </c>
-      <c r="B60" s="185"/>
+      <c r="B60" s="187"/>
       <c r="C60" s="116">
         <v>326000</v>
       </c>
@@ -2602,22 +2602,22 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="184" t="s">
+      <c r="A61" s="186" t="s">
         <v>191</v>
       </c>
-      <c r="B61" s="185"/>
+      <c r="B61" s="187"/>
       <c r="C61" s="116">
         <v>90000</v>
       </c>
-      <c r="D61" s="225" t="s">
+      <c r="D61" s="178" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="182" t="s">
+      <c r="A62" s="184" t="s">
         <v>161</v>
       </c>
-      <c r="B62" s="183"/>
+      <c r="B62" s="185"/>
       <c r="C62" s="116">
         <v>180000</v>
       </c>
@@ -2628,10 +2628,10 @@
       <c r="F62" s="37"/>
     </row>
     <row r="63" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="182" t="s">
+      <c r="A63" s="184" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="183"/>
+      <c r="B63" s="185"/>
       <c r="C63" s="116">
         <v>1745880</v>
       </c>
@@ -2642,10 +2642,10 @@
       <c r="F63" s="37"/>
     </row>
     <row r="64" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="184" t="s">
+      <c r="A64" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="B64" s="185"/>
+      <c r="B64" s="187"/>
       <c r="C64" s="116">
         <v>77600</v>
       </c>
@@ -2656,10 +2656,10 @@
       <c r="F64" s="37"/>
     </row>
     <row r="65" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="184" t="s">
+      <c r="A65" s="186" t="s">
         <v>171</v>
       </c>
-      <c r="B65" s="185"/>
+      <c r="B65" s="187"/>
       <c r="C65" s="116">
         <v>95700</v>
       </c>
@@ -2670,10 +2670,10 @@
       <c r="F65" s="37"/>
     </row>
     <row r="66" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="184" t="s">
+      <c r="A66" s="186" t="s">
         <v>169</v>
       </c>
-      <c r="B66" s="185"/>
+      <c r="B66" s="187"/>
       <c r="C66" s="116">
         <v>46200</v>
       </c>
@@ -2703,10 +2703,10 @@
       <c r="D68" s="76"/>
     </row>
     <row r="69" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="182" t="s">
+      <c r="A69" s="184" t="s">
         <v>74</v>
       </c>
-      <c r="B69" s="183"/>
+      <c r="B69" s="185"/>
       <c r="C69" s="116">
         <v>60000</v>
       </c>
@@ -2741,11 +2741,11 @@
       <c r="D72" s="82"/>
     </row>
     <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="187" t="s">
+      <c r="A73" s="181" t="s">
         <v>69</v>
       </c>
-      <c r="B73" s="188"/>
-      <c r="C73" s="189"/>
+      <c r="B73" s="182"/>
+      <c r="C73" s="183"/>
       <c r="D73" s="83"/>
     </row>
     <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2785,14 +2785,14 @@
       <c r="D78" s="89"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="179"/>
-      <c r="B79" s="180"/>
+      <c r="A79" s="188"/>
+      <c r="B79" s="189"/>
       <c r="C79" s="77"/>
       <c r="D79" s="75"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="179"/>
-      <c r="B80" s="180"/>
+      <c r="A80" s="188"/>
+      <c r="B80" s="189"/>
       <c r="C80" s="77"/>
       <c r="D80" s="75"/>
     </row>
@@ -2967,7 +2967,7 @@
         <v>199</v>
       </c>
       <c r="B107" s="147">
-        <v>1331900.92</v>
+        <v>1490504.61</v>
       </c>
       <c r="D107" s="129"/>
     </row>
@@ -2990,14 +2990,14 @@
       <c r="D111" s="130"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="178" t="s">
+      <c r="A112" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="B112" s="178"/>
+      <c r="B112" s="190"/>
     </row>
     <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="178"/>
-      <c r="B113" s="178"/>
+      <c r="A113" s="190"/>
+      <c r="B113" s="190"/>
     </row>
     <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="90" t="s">
@@ -3021,6 +3021,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A73:C73"/>
@@ -3035,13 +3042,6 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A112:B113"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3076,17 +3076,17 @@
   <sheetData>
     <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="196" t="s">
+      <c r="B1" s="192" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="198"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="194"/>
       <c r="K1" s="142" t="s">
         <v>4</v>
       </c>
@@ -3104,15 +3104,15 @@
     </row>
     <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="199"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="201"/>
+      <c r="B2" s="195"/>
+      <c r="C2" s="196"/>
+      <c r="D2" s="196"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="196"/>
+      <c r="G2" s="196"/>
+      <c r="H2" s="196"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="197"/>
       <c r="K2" s="144" t="s">
         <v>63</v>
       </c>
@@ -3125,90 +3125,90 @@
     </row>
     <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="213" t="s">
+      <c r="B3" s="211" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="214"/>
-      <c r="D3" s="214"/>
-      <c r="E3" s="214"/>
-      <c r="F3" s="214"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="214"/>
-      <c r="I3" s="214"/>
-      <c r="J3" s="214"/>
-      <c r="K3" s="214"/>
-      <c r="L3" s="214"/>
-      <c r="M3" s="214"/>
-      <c r="N3" s="214"/>
-      <c r="O3" s="215"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212"/>
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="213"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="190" t="s">
+      <c r="A4" s="214" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="192" t="s">
+      <c r="B4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="194" t="s">
+      <c r="D4" s="201" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="194" t="s">
+      <c r="E4" s="201" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="194" t="s">
+      <c r="F4" s="201" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="194" t="s">
+      <c r="G4" s="201" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="194" t="s">
+      <c r="H4" s="201" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="208" t="s">
+      <c r="I4" s="206" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="203" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="206" t="s">
+      <c r="K4" s="203" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="206" t="s">
+      <c r="L4" s="203" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="211" t="s">
+      <c r="M4" s="209" t="s">
         <v>58</v>
       </c>
       <c r="N4" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="202" t="s">
+      <c r="O4" s="198" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="37"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="191"/>
-      <c r="B5" s="193"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="195"/>
-      <c r="G5" s="195"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="210"/>
-      <c r="L5" s="207"/>
-      <c r="M5" s="212"/>
+      <c r="A5" s="215"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="202"/>
+      <c r="I5" s="207"/>
+      <c r="J5" s="204"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="204"/>
+      <c r="M5" s="210"/>
       <c r="N5" s="46" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="O5" s="203"/>
+      <c r="O5" s="199"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -5387,7 +5387,7 @@
       <c r="C44" s="118">
         <v>3301</v>
       </c>
-      <c r="D44" s="226" t="s">
+      <c r="D44" s="179" t="s">
         <v>125</v>
       </c>
       <c r="E44" s="51">
@@ -6584,87 +6584,92 @@
     </row>
     <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="204" t="s">
+      <c r="D69" s="200" t="s">
         <v>70</v>
       </c>
-      <c r="E69" s="204"/>
-      <c r="F69" s="204"/>
-      <c r="G69" s="204"/>
-      <c r="H69" s="204"/>
-      <c r="I69" s="204"/>
-      <c r="J69" s="204"/>
-      <c r="K69" s="204"/>
-      <c r="L69" s="204"/>
-      <c r="M69" s="204"/>
-      <c r="N69" s="204"/>
+      <c r="E69" s="200"/>
+      <c r="F69" s="200"/>
+      <c r="G69" s="200"/>
+      <c r="H69" s="200"/>
+      <c r="I69" s="200"/>
+      <c r="J69" s="200"/>
+      <c r="K69" s="200"/>
+      <c r="L69" s="200"/>
+      <c r="M69" s="200"/>
+      <c r="N69" s="200"/>
     </row>
     <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="204"/>
-      <c r="E70" s="204"/>
-      <c r="F70" s="204"/>
-      <c r="G70" s="204"/>
-      <c r="H70" s="204"/>
-      <c r="I70" s="204"/>
-      <c r="J70" s="204"/>
-      <c r="K70" s="204"/>
-      <c r="L70" s="204"/>
-      <c r="M70" s="204"/>
-      <c r="N70" s="204"/>
+      <c r="D70" s="200"/>
+      <c r="E70" s="200"/>
+      <c r="F70" s="200"/>
+      <c r="G70" s="200"/>
+      <c r="H70" s="200"/>
+      <c r="I70" s="200"/>
+      <c r="J70" s="200"/>
+      <c r="K70" s="200"/>
+      <c r="L70" s="200"/>
+      <c r="M70" s="200"/>
+      <c r="N70" s="200"/>
     </row>
     <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="204"/>
-      <c r="E71" s="204"/>
-      <c r="F71" s="204"/>
-      <c r="G71" s="204"/>
-      <c r="H71" s="204"/>
-      <c r="I71" s="204"/>
-      <c r="J71" s="204"/>
-      <c r="K71" s="204"/>
-      <c r="L71" s="204"/>
-      <c r="M71" s="204"/>
-      <c r="N71" s="204"/>
+      <c r="D71" s="200"/>
+      <c r="E71" s="200"/>
+      <c r="F71" s="200"/>
+      <c r="G71" s="200"/>
+      <c r="H71" s="200"/>
+      <c r="I71" s="200"/>
+      <c r="J71" s="200"/>
+      <c r="K71" s="200"/>
+      <c r="L71" s="200"/>
+      <c r="M71" s="200"/>
+      <c r="N71" s="200"/>
     </row>
     <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="204"/>
-      <c r="E72" s="204"/>
-      <c r="F72" s="204"/>
-      <c r="G72" s="204"/>
-      <c r="H72" s="204"/>
-      <c r="I72" s="204"/>
-      <c r="J72" s="204"/>
-      <c r="K72" s="204"/>
-      <c r="L72" s="204"/>
-      <c r="M72" s="204"/>
-      <c r="N72" s="204"/>
+      <c r="D72" s="200"/>
+      <c r="E72" s="200"/>
+      <c r="F72" s="200"/>
+      <c r="G72" s="200"/>
+      <c r="H72" s="200"/>
+      <c r="I72" s="200"/>
+      <c r="J72" s="200"/>
+      <c r="K72" s="200"/>
+      <c r="L72" s="200"/>
+      <c r="M72" s="200"/>
+      <c r="N72" s="200"/>
     </row>
     <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D73" s="204"/>
-      <c r="E73" s="204"/>
-      <c r="F73" s="204"/>
-      <c r="G73" s="204"/>
-      <c r="H73" s="204"/>
-      <c r="I73" s="204"/>
-      <c r="J73" s="204"/>
-      <c r="K73" s="204"/>
-      <c r="L73" s="204"/>
-      <c r="M73" s="204"/>
-      <c r="N73" s="204"/>
+      <c r="D73" s="200"/>
+      <c r="E73" s="200"/>
+      <c r="F73" s="200"/>
+      <c r="G73" s="200"/>
+      <c r="H73" s="200"/>
+      <c r="I73" s="200"/>
+      <c r="J73" s="200"/>
+      <c r="K73" s="200"/>
+      <c r="L73" s="200"/>
+      <c r="M73" s="200"/>
+      <c r="N73" s="200"/>
     </row>
     <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D74" s="204"/>
-      <c r="E74" s="204"/>
-      <c r="F74" s="204"/>
-      <c r="G74" s="204"/>
-      <c r="H74" s="204"/>
-      <c r="I74" s="204"/>
-      <c r="J74" s="204"/>
-      <c r="K74" s="204"/>
-      <c r="L74" s="204"/>
-      <c r="M74" s="204"/>
-      <c r="N74" s="204"/>
+      <c r="D74" s="200"/>
+      <c r="E74" s="200"/>
+      <c r="F74" s="200"/>
+      <c r="G74" s="200"/>
+      <c r="H74" s="200"/>
+      <c r="I74" s="200"/>
+      <c r="J74" s="200"/>
+      <c r="K74" s="200"/>
+      <c r="L74" s="200"/>
+      <c r="M74" s="200"/>
+      <c r="N74" s="200"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D69:N74"/>
@@ -6677,11 +6682,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6723,34 +6723,34 @@
       <c r="J5" s="162"/>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C6" s="216" t="s">
+      <c r="C6" s="218" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="217"/>
-      <c r="E6" s="217"/>
-      <c r="F6" s="217"/>
-      <c r="G6" s="217"/>
-      <c r="H6" s="218"/>
+      <c r="D6" s="219"/>
+      <c r="E6" s="219"/>
+      <c r="F6" s="219"/>
+      <c r="G6" s="219"/>
+      <c r="H6" s="220"/>
       <c r="I6" s="162"/>
       <c r="J6" s="162"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C7" s="219"/>
-      <c r="D7" s="220"/>
-      <c r="E7" s="220"/>
-      <c r="F7" s="220"/>
-      <c r="G7" s="220"/>
-      <c r="H7" s="221"/>
+      <c r="C7" s="221"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="223"/>
       <c r="I7" s="162"/>
       <c r="J7" s="162"/>
     </row>
     <row r="8" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="222"/>
-      <c r="D8" s="223"/>
-      <c r="E8" s="223"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="223"/>
-      <c r="H8" s="224"/>
+      <c r="C8" s="224"/>
+      <c r="D8" s="225"/>
+      <c r="E8" s="225"/>
+      <c r="F8" s="225"/>
+      <c r="G8" s="225"/>
+      <c r="H8" s="226"/>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" s="104"/>
@@ -6791,32 +6791,32 @@
       <c r="J13" s="162"/>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C14" s="216" t="s">
+      <c r="C14" s="218" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-      <c r="F14" s="217"/>
-      <c r="G14" s="217"/>
-      <c r="H14" s="218"/>
+      <c r="D14" s="219"/>
+      <c r="E14" s="219"/>
+      <c r="F14" s="219"/>
+      <c r="G14" s="219"/>
+      <c r="H14" s="220"/>
       <c r="I14" s="162"/>
       <c r="J14" s="162"/>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C15" s="219"/>
-      <c r="D15" s="220"/>
-      <c r="E15" s="220"/>
-      <c r="F15" s="220"/>
-      <c r="G15" s="220"/>
-      <c r="H15" s="221"/>
+      <c r="C15" s="221"/>
+      <c r="D15" s="222"/>
+      <c r="E15" s="222"/>
+      <c r="F15" s="222"/>
+      <c r="G15" s="222"/>
+      <c r="H15" s="223"/>
     </row>
     <row r="16" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="222"/>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-      <c r="F16" s="223"/>
-      <c r="G16" s="223"/>
-      <c r="H16" s="224"/>
+      <c r="C16" s="224"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225"/>
+      <c r="G16" s="225"/>
+      <c r="H16" s="226"/>
     </row>
     <row r="18" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="3:11" x14ac:dyDescent="0.25">
@@ -6853,36 +6853,36 @@
       <c r="K21" s="162"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="216" t="s">
+      <c r="C22" s="218" t="s">
         <v>159</v>
       </c>
-      <c r="D22" s="217"/>
-      <c r="E22" s="217"/>
-      <c r="F22" s="217"/>
-      <c r="G22" s="217"/>
-      <c r="H22" s="218"/>
+      <c r="D22" s="219"/>
+      <c r="E22" s="219"/>
+      <c r="F22" s="219"/>
+      <c r="G22" s="219"/>
+      <c r="H22" s="220"/>
       <c r="I22" s="162"/>
       <c r="J22" s="162"/>
       <c r="K22" s="162"/>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="219"/>
-      <c r="D23" s="220"/>
-      <c r="E23" s="220"/>
-      <c r="F23" s="220"/>
-      <c r="G23" s="220"/>
-      <c r="H23" s="221"/>
+      <c r="C23" s="221"/>
+      <c r="D23" s="222"/>
+      <c r="E23" s="222"/>
+      <c r="F23" s="222"/>
+      <c r="G23" s="222"/>
+      <c r="H23" s="223"/>
       <c r="I23" s="162"/>
       <c r="J23" s="162"/>
       <c r="K23" s="162"/>
     </row>
     <row r="24" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="222"/>
-      <c r="D24" s="223"/>
-      <c r="E24" s="223"/>
-      <c r="F24" s="223"/>
-      <c r="G24" s="223"/>
-      <c r="H24" s="224"/>
+      <c r="C24" s="224"/>
+      <c r="D24" s="225"/>
+      <c r="E24" s="225"/>
+      <c r="F24" s="225"/>
+      <c r="G24" s="225"/>
+      <c r="H24" s="226"/>
     </row>
     <row r="26" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="3:11" x14ac:dyDescent="0.25">
@@ -6915,34 +6915,34 @@
       <c r="J29" s="162"/>
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C30" s="216" t="s">
+      <c r="C30" s="218" t="s">
         <v>174</v>
       </c>
-      <c r="D30" s="217"/>
-      <c r="E30" s="217"/>
-      <c r="F30" s="217"/>
-      <c r="G30" s="217"/>
-      <c r="H30" s="218"/>
+      <c r="D30" s="219"/>
+      <c r="E30" s="219"/>
+      <c r="F30" s="219"/>
+      <c r="G30" s="219"/>
+      <c r="H30" s="220"/>
       <c r="I30" s="162"/>
       <c r="J30" s="162"/>
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C31" s="219"/>
-      <c r="D31" s="220"/>
-      <c r="E31" s="220"/>
-      <c r="F31" s="220"/>
-      <c r="G31" s="220"/>
-      <c r="H31" s="221"/>
+      <c r="C31" s="221"/>
+      <c r="D31" s="222"/>
+      <c r="E31" s="222"/>
+      <c r="F31" s="222"/>
+      <c r="G31" s="222"/>
+      <c r="H31" s="223"/>
       <c r="I31" s="162"/>
       <c r="J31" s="162"/>
     </row>
     <row r="32" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="222"/>
-      <c r="D32" s="223"/>
-      <c r="E32" s="223"/>
-      <c r="F32" s="223"/>
-      <c r="G32" s="223"/>
-      <c r="H32" s="224"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="225"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="226"/>
     </row>
     <row r="34" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="3:11" x14ac:dyDescent="0.25">
@@ -6977,34 +6977,34 @@
       <c r="J37" s="162"/>
     </row>
     <row r="38" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C38" s="216" t="s">
+      <c r="C38" s="218" t="s">
         <v>176</v>
       </c>
-      <c r="D38" s="217"/>
-      <c r="E38" s="217"/>
-      <c r="F38" s="217"/>
-      <c r="G38" s="217"/>
-      <c r="H38" s="218"/>
+      <c r="D38" s="219"/>
+      <c r="E38" s="219"/>
+      <c r="F38" s="219"/>
+      <c r="G38" s="219"/>
+      <c r="H38" s="220"/>
       <c r="I38" s="162"/>
       <c r="J38" s="162"/>
     </row>
     <row r="39" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C39" s="219"/>
-      <c r="D39" s="220"/>
-      <c r="E39" s="220"/>
-      <c r="F39" s="220"/>
-      <c r="G39" s="220"/>
-      <c r="H39" s="221"/>
+      <c r="C39" s="221"/>
+      <c r="D39" s="222"/>
+      <c r="E39" s="222"/>
+      <c r="F39" s="222"/>
+      <c r="G39" s="222"/>
+      <c r="H39" s="223"/>
       <c r="I39" s="162"/>
       <c r="J39" s="162"/>
     </row>
     <row r="40" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="222"/>
-      <c r="D40" s="223"/>
-      <c r="E40" s="223"/>
-      <c r="F40" s="223"/>
-      <c r="G40" s="223"/>
-      <c r="H40" s="224"/>
+      <c r="C40" s="224"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
     </row>
     <row r="42" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="43" spans="3:11" x14ac:dyDescent="0.25">
@@ -7044,36 +7044,36 @@
       <c r="K45" s="162"/>
     </row>
     <row r="46" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C46" s="216" t="s">
+      <c r="C46" s="218" t="s">
         <v>180</v>
       </c>
-      <c r="D46" s="217"/>
-      <c r="E46" s="217"/>
-      <c r="F46" s="217"/>
-      <c r="G46" s="217"/>
-      <c r="H46" s="218"/>
+      <c r="D46" s="219"/>
+      <c r="E46" s="219"/>
+      <c r="F46" s="219"/>
+      <c r="G46" s="219"/>
+      <c r="H46" s="220"/>
       <c r="I46" s="162"/>
       <c r="J46" s="162"/>
       <c r="K46" s="162"/>
     </row>
     <row r="47" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C47" s="219"/>
-      <c r="D47" s="220"/>
-      <c r="E47" s="220"/>
-      <c r="F47" s="220"/>
-      <c r="G47" s="220"/>
-      <c r="H47" s="221"/>
+      <c r="C47" s="221"/>
+      <c r="D47" s="222"/>
+      <c r="E47" s="222"/>
+      <c r="F47" s="222"/>
+      <c r="G47" s="222"/>
+      <c r="H47" s="223"/>
       <c r="I47" s="162"/>
       <c r="J47" s="162"/>
       <c r="K47" s="162"/>
     </row>
     <row r="48" spans="3:11" ht="43.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="222"/>
-      <c r="D48" s="223"/>
-      <c r="E48" s="223"/>
-      <c r="F48" s="223"/>
-      <c r="G48" s="223"/>
-      <c r="H48" s="224"/>
+      <c r="C48" s="224"/>
+      <c r="D48" s="225"/>
+      <c r="E48" s="225"/>
+      <c r="F48" s="225"/>
+      <c r="G48" s="225"/>
+      <c r="H48" s="226"/>
       <c r="I48" s="162"/>
       <c r="J48" s="162"/>
       <c r="K48" s="162"/>

--- a/2026/GALERIA MITRE/Mayo/Mayo MITRE.xlsx
+++ b/2026/GALERIA MITRE/Mayo/Mayo MITRE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9676EC2-6D8E-4979-B090-74A30369A36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117F14AC-831E-48E4-BE5B-B67022C38BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -839,7 +839,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -939,6 +939,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF33CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1302,7 +1308,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1547,158 +1553,159 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="18" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1707,6 +1714,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF33CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2092,68 +2104,68 @@
       <c r="D3" s="98"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="193" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="180"/>
+      <c r="B4" s="193"/>
       <c r="C4" s="99"/>
       <c r="D4" s="99"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="180"/>
-      <c r="B5" s="180"/>
+      <c r="A5" s="193"/>
+      <c r="B5" s="193"/>
       <c r="C5" s="99"/>
       <c r="D5" s="99"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="180"/>
-      <c r="B6" s="180"/>
+      <c r="A6" s="193"/>
+      <c r="B6" s="193"/>
       <c r="C6" s="99"/>
       <c r="D6" s="99"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="180"/>
-      <c r="B7" s="180"/>
+      <c r="A7" s="193"/>
+      <c r="B7" s="193"/>
       <c r="C7" s="99"/>
       <c r="D7" s="99"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="191" t="s">
+      <c r="B9" s="188" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="191"/>
+      <c r="B10" s="188"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="191"/>
+      <c r="B11" s="188"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="180" t="s">
+      <c r="A14" s="193" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="180"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="180"/>
+      <c r="B14" s="193"/>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="180"/>
-      <c r="B15" s="180"/>
-      <c r="C15" s="180"/>
-      <c r="D15" s="180"/>
+      <c r="A15" s="193"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
     </row>
     <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="180"/>
-      <c r="B16" s="180"/>
-      <c r="C16" s="180"/>
-      <c r="D16" s="180"/>
+      <c r="A16" s="193"/>
+      <c r="B16" s="193"/>
+      <c r="C16" s="193"/>
+      <c r="D16" s="193"/>
     </row>
     <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="180"/>
-      <c r="B17" s="180"/>
-      <c r="C17" s="180"/>
-      <c r="D17" s="180"/>
+      <c r="A17" s="193"/>
+      <c r="B17" s="193"/>
+      <c r="C17" s="193"/>
+      <c r="D17" s="193"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2177,10 +2189,10 @@
       <c r="D22" s="23"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="188" t="s">
+      <c r="A23" s="186" t="s">
         <v>182</v>
       </c>
-      <c r="B23" s="189"/>
+      <c r="B23" s="187"/>
       <c r="C23" s="113">
         <v>939981.1</v>
       </c>
@@ -2219,10 +2231,10 @@
       <c r="D26" s="43"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="188" t="s">
+      <c r="A27" s="186" t="s">
         <v>183</v>
       </c>
-      <c r="B27" s="189"/>
+      <c r="B27" s="187"/>
       <c r="C27" s="113">
         <v>849606.52</v>
       </c>
@@ -2364,10 +2376,10 @@
       <c r="D40" s="49"/>
     </row>
     <row r="41" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="184" t="s">
+      <c r="A41" s="189" t="s">
         <v>132</v>
       </c>
-      <c r="B41" s="185"/>
+      <c r="B41" s="190"/>
       <c r="C41" s="127">
         <v>111379</v>
       </c>
@@ -2406,10 +2418,10 @@
       <c r="F44" s="104"/>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="184" t="s">
+      <c r="A45" s="189" t="s">
         <v>172</v>
       </c>
-      <c r="B45" s="185"/>
+      <c r="B45" s="190"/>
       <c r="C45" s="131">
         <v>11596.99</v>
       </c>
@@ -2419,10 +2431,10 @@
       <c r="F45" s="104"/>
     </row>
     <row r="46" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="184" t="s">
+      <c r="A46" s="189" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="185"/>
+      <c r="B46" s="190"/>
       <c r="C46" s="131">
         <v>11930.96</v>
       </c>
@@ -2570,10 +2582,10 @@
       <c r="D58" s="76"/>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="186" t="s">
+      <c r="A59" s="191" t="s">
         <v>162</v>
       </c>
-      <c r="B59" s="187"/>
+      <c r="B59" s="192"/>
       <c r="C59" s="116">
         <v>171600</v>
       </c>
@@ -2582,10 +2594,10 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="186" t="s">
+      <c r="A60" s="191" t="s">
         <v>164</v>
       </c>
-      <c r="B60" s="187"/>
+      <c r="B60" s="192"/>
       <c r="C60" s="116">
         <v>326000</v>
       </c>
@@ -2594,10 +2606,10 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="186" t="s">
+      <c r="A61" s="191" t="s">
         <v>180</v>
       </c>
-      <c r="B61" s="187"/>
+      <c r="B61" s="192"/>
       <c r="C61" s="116">
         <v>90000</v>
       </c>
@@ -2606,10 +2618,10 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="184" t="s">
+      <c r="A62" s="189" t="s">
         <v>159</v>
       </c>
-      <c r="B62" s="185"/>
+      <c r="B62" s="190"/>
       <c r="C62" s="116">
         <v>180000</v>
       </c>
@@ -2620,10 +2632,10 @@
       <c r="F62" s="37"/>
     </row>
     <row r="63" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="184" t="s">
+      <c r="A63" s="189" t="s">
         <v>173</v>
       </c>
-      <c r="B63" s="185"/>
+      <c r="B63" s="190"/>
       <c r="C63" s="116">
         <v>1745880</v>
       </c>
@@ -2634,10 +2646,10 @@
       <c r="F63" s="37"/>
     </row>
     <row r="64" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="186" t="s">
+      <c r="A64" s="191" t="s">
         <v>168</v>
       </c>
-      <c r="B64" s="187"/>
+      <c r="B64" s="192"/>
       <c r="C64" s="116">
         <v>77600</v>
       </c>
@@ -2648,10 +2660,10 @@
       <c r="F64" s="37"/>
     </row>
     <row r="65" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="186" t="s">
+      <c r="A65" s="191" t="s">
         <v>169</v>
       </c>
-      <c r="B65" s="187"/>
+      <c r="B65" s="192"/>
       <c r="C65" s="116">
         <v>95700</v>
       </c>
@@ -2662,10 +2674,10 @@
       <c r="F65" s="37"/>
     </row>
     <row r="66" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="186" t="s">
+      <c r="A66" s="191" t="s">
         <v>167</v>
       </c>
-      <c r="B66" s="187"/>
+      <c r="B66" s="192"/>
       <c r="C66" s="116">
         <v>46200</v>
       </c>
@@ -2695,10 +2707,10 @@
       <c r="D68" s="76"/>
     </row>
     <row r="69" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="184" t="s">
+      <c r="A69" s="189" t="s">
         <v>74</v>
       </c>
-      <c r="B69" s="185"/>
+      <c r="B69" s="190"/>
       <c r="C69" s="116">
         <v>60000</v>
       </c>
@@ -2733,11 +2745,11 @@
       <c r="D72" s="82"/>
     </row>
     <row r="73" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="181" t="s">
+      <c r="A73" s="194" t="s">
         <v>69</v>
       </c>
-      <c r="B73" s="182"/>
-      <c r="C73" s="183"/>
+      <c r="B73" s="195"/>
+      <c r="C73" s="196"/>
       <c r="D73" s="83"/>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2777,14 +2789,14 @@
       <c r="D78" s="89"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="188"/>
-      <c r="B79" s="189"/>
+      <c r="A79" s="186"/>
+      <c r="B79" s="187"/>
       <c r="C79" s="77"/>
       <c r="D79" s="75"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="188"/>
-      <c r="B80" s="189"/>
+      <c r="A80" s="186"/>
+      <c r="B80" s="187"/>
       <c r="C80" s="77"/>
       <c r="D80" s="75"/>
     </row>
@@ -2982,14 +2994,14 @@
       <c r="D111" s="130"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="190" t="s">
+      <c r="A112" s="185" t="s">
         <v>50</v>
       </c>
-      <c r="B112" s="190"/>
+      <c r="B112" s="185"/>
     </row>
     <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="190"/>
-      <c r="B113" s="190"/>
+      <c r="A113" s="185"/>
+      <c r="B113" s="185"/>
     </row>
     <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="90" t="s">
@@ -3013,13 +3025,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A112:B113"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A73:C73"/>
@@ -3034,6 +3039,13 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3068,17 +3080,17 @@
   <sheetData>
     <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="192" t="s">
+      <c r="B1" s="203" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="194"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="205"/>
       <c r="K1" s="142" t="s">
         <v>4</v>
       </c>
@@ -3096,15 +3108,15 @@
     </row>
     <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
-      <c r="B2" s="195"/>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="197"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="207"/>
+      <c r="J2" s="208"/>
       <c r="K2" s="144" t="s">
         <v>63</v>
       </c>
@@ -3117,28 +3129,28 @@
     </row>
     <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="211" t="s">
+      <c r="B3" s="220" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="212"/>
-      <c r="I3" s="212"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="M3" s="212"/>
-      <c r="N3" s="212"/>
-      <c r="O3" s="213"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="221"/>
+      <c r="I3" s="221"/>
+      <c r="J3" s="221"/>
+      <c r="K3" s="221"/>
+      <c r="L3" s="221"/>
+      <c r="M3" s="221"/>
+      <c r="N3" s="221"/>
+      <c r="O3" s="222"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="214" t="s">
+      <c r="A4" s="197" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="199" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="201" t="s">
@@ -3159,48 +3171,48 @@
       <c r="H4" s="201" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="206" t="s">
+      <c r="I4" s="215" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="203" t="s">
+      <c r="J4" s="213" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="203" t="s">
+      <c r="K4" s="213" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="213" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="209" t="s">
+      <c r="M4" s="218" t="s">
         <v>58</v>
       </c>
       <c r="N4" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="198" t="s">
+      <c r="O4" s="209" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="37"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="215"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="207"/>
-      <c r="J5" s="204"/>
-      <c r="K5" s="208"/>
-      <c r="L5" s="204"/>
-      <c r="M5" s="210"/>
+      <c r="A5" s="198"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="202"/>
+      <c r="F5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="214"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="214"/>
+      <c r="M5" s="219"/>
       <c r="N5" s="46" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="O5" s="199"/>
+      <c r="O5" s="210"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -4052,14 +4064,14 @@
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="229">
+      <c r="B21" s="180">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="C21" s="229" t="s">
+      <c r="C21" s="180" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="229" t="s">
+      <c r="D21" s="180" t="s">
         <v>87</v>
       </c>
       <c r="E21" s="51">
@@ -4412,7 +4424,7 @@
       <c r="F27" s="52">
         <v>5904294.21</v>
       </c>
-      <c r="G27" s="53">
+      <c r="G27" s="234">
         <v>0</v>
       </c>
       <c r="H27" s="54"/>
@@ -4983,7 +4995,7 @@
       <c r="F37" s="53">
         <v>29842.31</v>
       </c>
-      <c r="G37" s="53"/>
+      <c r="G37" s="234"/>
       <c r="H37" s="54"/>
       <c r="I37" s="55">
         <f t="shared" si="2"/>
@@ -5040,7 +5052,7 @@
       <c r="F38" s="52">
         <v>29842.32</v>
       </c>
-      <c r="G38" s="53"/>
+      <c r="G38" s="234"/>
       <c r="H38" s="54"/>
       <c r="I38" s="55">
         <f t="shared" si="2"/>
@@ -5156,7 +5168,7 @@
       <c r="F40" s="52">
         <v>85924.34</v>
       </c>
-      <c r="G40" s="53"/>
+      <c r="G40" s="234"/>
       <c r="H40" s="54"/>
       <c r="I40" s="55">
         <f t="shared" si="2"/>
@@ -5333,7 +5345,7 @@
       <c r="F43" s="52">
         <v>63286.37</v>
       </c>
-      <c r="G43" s="53"/>
+      <c r="G43" s="234"/>
       <c r="H43" s="54"/>
       <c r="I43" s="55">
         <f t="shared" si="2"/>
@@ -6307,7 +6319,7 @@
       <c r="F61" s="52">
         <v>1032605.55</v>
       </c>
-      <c r="G61" s="53">
+      <c r="G61" s="234">
         <v>300000</v>
       </c>
       <c r="H61" s="61"/>
@@ -6576,92 +6588,87 @@
     </row>
     <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D69" s="200" t="s">
+      <c r="D69" s="211" t="s">
         <v>70</v>
       </c>
-      <c r="E69" s="200"/>
-      <c r="F69" s="200"/>
-      <c r="G69" s="200"/>
-      <c r="H69" s="200"/>
-      <c r="I69" s="200"/>
-      <c r="J69" s="200"/>
-      <c r="K69" s="200"/>
-      <c r="L69" s="200"/>
-      <c r="M69" s="200"/>
-      <c r="N69" s="200"/>
+      <c r="E69" s="211"/>
+      <c r="F69" s="211"/>
+      <c r="G69" s="211"/>
+      <c r="H69" s="211"/>
+      <c r="I69" s="211"/>
+      <c r="J69" s="211"/>
+      <c r="K69" s="211"/>
+      <c r="L69" s="211"/>
+      <c r="M69" s="211"/>
+      <c r="N69" s="211"/>
     </row>
     <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D70" s="200"/>
-      <c r="E70" s="200"/>
-      <c r="F70" s="200"/>
-      <c r="G70" s="200"/>
-      <c r="H70" s="200"/>
-      <c r="I70" s="200"/>
-      <c r="J70" s="200"/>
-      <c r="K70" s="200"/>
-      <c r="L70" s="200"/>
-      <c r="M70" s="200"/>
-      <c r="N70" s="200"/>
+      <c r="D70" s="211"/>
+      <c r="E70" s="211"/>
+      <c r="F70" s="211"/>
+      <c r="G70" s="211"/>
+      <c r="H70" s="211"/>
+      <c r="I70" s="211"/>
+      <c r="J70" s="211"/>
+      <c r="K70" s="211"/>
+      <c r="L70" s="211"/>
+      <c r="M70" s="211"/>
+      <c r="N70" s="211"/>
     </row>
     <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="200"/>
-      <c r="E71" s="200"/>
-      <c r="F71" s="200"/>
-      <c r="G71" s="200"/>
-      <c r="H71" s="200"/>
-      <c r="I71" s="200"/>
-      <c r="J71" s="200"/>
-      <c r="K71" s="200"/>
-      <c r="L71" s="200"/>
-      <c r="M71" s="200"/>
-      <c r="N71" s="200"/>
+      <c r="D71" s="211"/>
+      <c r="E71" s="211"/>
+      <c r="F71" s="211"/>
+      <c r="G71" s="211"/>
+      <c r="H71" s="211"/>
+      <c r="I71" s="211"/>
+      <c r="J71" s="211"/>
+      <c r="K71" s="211"/>
+      <c r="L71" s="211"/>
+      <c r="M71" s="211"/>
+      <c r="N71" s="211"/>
     </row>
     <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="200"/>
-      <c r="E72" s="200"/>
-      <c r="F72" s="200"/>
-      <c r="G72" s="200"/>
-      <c r="H72" s="200"/>
-      <c r="I72" s="200"/>
-      <c r="J72" s="200"/>
-      <c r="K72" s="200"/>
-      <c r="L72" s="200"/>
-      <c r="M72" s="200"/>
-      <c r="N72" s="200"/>
+      <c r="D72" s="211"/>
+      <c r="E72" s="211"/>
+      <c r="F72" s="211"/>
+      <c r="G72" s="211"/>
+      <c r="H72" s="211"/>
+      <c r="I72" s="211"/>
+      <c r="J72" s="211"/>
+      <c r="K72" s="211"/>
+      <c r="L72" s="211"/>
+      <c r="M72" s="211"/>
+      <c r="N72" s="211"/>
     </row>
     <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="200"/>
-      <c r="E73" s="200"/>
-      <c r="F73" s="200"/>
-      <c r="G73" s="200"/>
-      <c r="H73" s="200"/>
-      <c r="I73" s="200"/>
-      <c r="J73" s="200"/>
-      <c r="K73" s="200"/>
-      <c r="L73" s="200"/>
-      <c r="M73" s="200"/>
-      <c r="N73" s="200"/>
+      <c r="D73" s="211"/>
+      <c r="E73" s="211"/>
+      <c r="F73" s="211"/>
+      <c r="G73" s="211"/>
+      <c r="H73" s="211"/>
+      <c r="I73" s="211"/>
+      <c r="J73" s="211"/>
+      <c r="K73" s="211"/>
+      <c r="L73" s="211"/>
+      <c r="M73" s="211"/>
+      <c r="N73" s="211"/>
     </row>
     <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="200"/>
-      <c r="E74" s="200"/>
-      <c r="F74" s="200"/>
-      <c r="G74" s="200"/>
-      <c r="H74" s="200"/>
-      <c r="I74" s="200"/>
-      <c r="J74" s="200"/>
-      <c r="K74" s="200"/>
-      <c r="L74" s="200"/>
-      <c r="M74" s="200"/>
-      <c r="N74" s="200"/>
+      <c r="D74" s="211"/>
+      <c r="E74" s="211"/>
+      <c r="F74" s="211"/>
+      <c r="G74" s="211"/>
+      <c r="H74" s="211"/>
+      <c r="I74" s="211"/>
+      <c r="J74" s="211"/>
+      <c r="K74" s="211"/>
+      <c r="L74" s="211"/>
+      <c r="M74" s="211"/>
+      <c r="N74" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D69:N74"/>
@@ -6674,6 +6681,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B3:O3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6715,34 +6727,34 @@
       <c r="J5" s="104"/>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="220" t="s">
+      <c r="C6" s="223" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="221"/>
-      <c r="E6" s="221"/>
-      <c r="F6" s="221"/>
-      <c r="G6" s="221"/>
-      <c r="H6" s="222"/>
+      <c r="D6" s="224"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="224"/>
+      <c r="G6" s="224"/>
+      <c r="H6" s="225"/>
       <c r="I6" s="104"/>
       <c r="J6" s="104"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="223"/>
-      <c r="D7" s="224"/>
-      <c r="E7" s="224"/>
-      <c r="F7" s="224"/>
-      <c r="G7" s="224"/>
-      <c r="H7" s="225"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="227"/>
+      <c r="E7" s="227"/>
+      <c r="F7" s="227"/>
+      <c r="G7" s="227"/>
+      <c r="H7" s="228"/>
       <c r="I7" s="104"/>
       <c r="J7" s="104"/>
     </row>
     <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="226"/>
-      <c r="D8" s="227"/>
-      <c r="E8" s="227"/>
-      <c r="F8" s="227"/>
-      <c r="G8" s="227"/>
-      <c r="H8" s="228"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="E8" s="230"/>
+      <c r="F8" s="230"/>
+      <c r="G8" s="230"/>
+      <c r="H8" s="231"/>
       <c r="I8" s="104"/>
       <c r="J8" s="104"/>
     </row>
@@ -6783,30 +6795,30 @@
       <c r="H13" s="150"/>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="220" t="s">
+      <c r="C14" s="223" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="221"/>
-      <c r="E14" s="221"/>
-      <c r="F14" s="221"/>
-      <c r="G14" s="221"/>
-      <c r="H14" s="222"/>
+      <c r="D14" s="224"/>
+      <c r="E14" s="224"/>
+      <c r="F14" s="224"/>
+      <c r="G14" s="224"/>
+      <c r="H14" s="225"/>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="223"/>
-      <c r="D15" s="224"/>
-      <c r="E15" s="224"/>
-      <c r="F15" s="224"/>
-      <c r="G15" s="224"/>
-      <c r="H15" s="225"/>
+      <c r="C15" s="226"/>
+      <c r="D15" s="227"/>
+      <c r="E15" s="227"/>
+      <c r="F15" s="227"/>
+      <c r="G15" s="227"/>
+      <c r="H15" s="228"/>
     </row>
     <row r="16" spans="3:10" ht="67.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="226"/>
-      <c r="D16" s="227"/>
-      <c r="E16" s="227"/>
-      <c r="F16" s="227"/>
-      <c r="G16" s="227"/>
-      <c r="H16" s="228"/>
+      <c r="C16" s="229"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="230"/>
+      <c r="F16" s="230"/>
+      <c r="G16" s="230"/>
+      <c r="H16" s="231"/>
     </row>
     <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="3:8" x14ac:dyDescent="0.3">
@@ -6837,30 +6849,30 @@
       <c r="H21" s="150"/>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C22" s="220" t="s">
+      <c r="C22" s="223" t="s">
         <v>193</v>
       </c>
-      <c r="D22" s="221"/>
-      <c r="E22" s="221"/>
-      <c r="F22" s="221"/>
-      <c r="G22" s="221"/>
-      <c r="H22" s="222"/>
+      <c r="D22" s="224"/>
+      <c r="E22" s="224"/>
+      <c r="F22" s="224"/>
+      <c r="G22" s="224"/>
+      <c r="H22" s="225"/>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="223"/>
-      <c r="D23" s="224"/>
-      <c r="E23" s="224"/>
-      <c r="F23" s="224"/>
-      <c r="G23" s="224"/>
-      <c r="H23" s="225"/>
+      <c r="C23" s="226"/>
+      <c r="D23" s="227"/>
+      <c r="E23" s="227"/>
+      <c r="F23" s="227"/>
+      <c r="G23" s="227"/>
+      <c r="H23" s="228"/>
     </row>
     <row r="24" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C24" s="226"/>
-      <c r="D24" s="227"/>
-      <c r="E24" s="227"/>
-      <c r="F24" s="227"/>
-      <c r="G24" s="227"/>
-      <c r="H24" s="228"/>
+      <c r="C24" s="229"/>
+      <c r="D24" s="230"/>
+      <c r="E24" s="230"/>
+      <c r="F24" s="230"/>
+      <c r="G24" s="230"/>
+      <c r="H24" s="231"/>
     </row>
     <row r="26" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="3:8" x14ac:dyDescent="0.3">
@@ -6891,30 +6903,30 @@
       <c r="H29" s="150"/>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C30" s="220" t="s">
+      <c r="C30" s="223" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="221"/>
-      <c r="E30" s="221"/>
-      <c r="F30" s="221"/>
-      <c r="G30" s="221"/>
-      <c r="H30" s="222"/>
+      <c r="D30" s="224"/>
+      <c r="E30" s="224"/>
+      <c r="F30" s="224"/>
+      <c r="G30" s="224"/>
+      <c r="H30" s="225"/>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C31" s="223"/>
-      <c r="D31" s="224"/>
-      <c r="E31" s="224"/>
-      <c r="F31" s="224"/>
-      <c r="G31" s="224"/>
-      <c r="H31" s="225"/>
+      <c r="C31" s="226"/>
+      <c r="D31" s="227"/>
+      <c r="E31" s="227"/>
+      <c r="F31" s="227"/>
+      <c r="G31" s="227"/>
+      <c r="H31" s="228"/>
     </row>
     <row r="32" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="226"/>
-      <c r="D32" s="227"/>
-      <c r="E32" s="227"/>
-      <c r="F32" s="227"/>
-      <c r="G32" s="227"/>
-      <c r="H32" s="228"/>
+      <c r="C32" s="229"/>
+      <c r="D32" s="230"/>
+      <c r="E32" s="230"/>
+      <c r="F32" s="230"/>
+      <c r="G32" s="230"/>
+      <c r="H32" s="231"/>
     </row>
     <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -6929,12 +6941,12 @@
       <c r="F35" s="148"/>
       <c r="G35" s="148"/>
       <c r="H35" s="149"/>
-      <c r="I35" s="218" t="s">
+      <c r="I35" s="232" t="s">
         <v>198</v>
       </c>
-      <c r="J35" s="219"/>
-      <c r="K35" s="219"/>
-      <c r="L35" s="219"/>
+      <c r="J35" s="233"/>
+      <c r="K35" s="233"/>
+      <c r="L35" s="233"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C36" s="160" t="s">
@@ -6944,57 +6956,57 @@
         <v>196</v>
       </c>
       <c r="H36" s="150"/>
-      <c r="I36" s="218"/>
-      <c r="J36" s="219"/>
-      <c r="K36" s="219"/>
-      <c r="L36" s="219"/>
+      <c r="I36" s="232"/>
+      <c r="J36" s="233"/>
+      <c r="K36" s="233"/>
+      <c r="L36" s="233"/>
     </row>
     <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C37" s="160"/>
       <c r="D37" s="161"/>
       <c r="H37" s="150"/>
-      <c r="I37" s="218"/>
-      <c r="J37" s="219"/>
-      <c r="K37" s="219"/>
-      <c r="L37" s="219"/>
+      <c r="I37" s="232"/>
+      <c r="J37" s="233"/>
+      <c r="K37" s="233"/>
+      <c r="L37" s="233"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C38" s="220" t="s">
+      <c r="C38" s="223" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="221"/>
-      <c r="E38" s="221"/>
-      <c r="F38" s="221"/>
-      <c r="G38" s="221"/>
-      <c r="H38" s="222"/>
-      <c r="I38" s="218"/>
-      <c r="J38" s="219"/>
-      <c r="K38" s="219"/>
-      <c r="L38" s="219"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="224"/>
+      <c r="H38" s="225"/>
+      <c r="I38" s="232"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C39" s="223"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="224"/>
-      <c r="F39" s="224"/>
-      <c r="G39" s="224"/>
-      <c r="H39" s="225"/>
-      <c r="I39" s="218"/>
-      <c r="J39" s="219"/>
-      <c r="K39" s="219"/>
-      <c r="L39" s="219"/>
+      <c r="C39" s="226"/>
+      <c r="D39" s="227"/>
+      <c r="E39" s="227"/>
+      <c r="F39" s="227"/>
+      <c r="G39" s="227"/>
+      <c r="H39" s="228"/>
+      <c r="I39" s="232"/>
+      <c r="J39" s="233"/>
+      <c r="K39" s="233"/>
+      <c r="L39" s="233"/>
     </row>
     <row r="40" spans="1:12" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="226"/>
-      <c r="D40" s="227"/>
-      <c r="E40" s="227"/>
-      <c r="F40" s="227"/>
-      <c r="G40" s="227"/>
-      <c r="H40" s="228"/>
-      <c r="I40" s="218"/>
-      <c r="J40" s="219"/>
-      <c r="K40" s="219"/>
-      <c r="L40" s="219"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
     </row>
     <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="125"/>
@@ -7027,37 +7039,37 @@
       <c r="H45" s="150"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C46" s="220" t="s">
+      <c r="C46" s="223" t="s">
         <v>200</v>
       </c>
-      <c r="D46" s="221"/>
-      <c r="E46" s="221"/>
-      <c r="F46" s="221"/>
-      <c r="G46" s="221"/>
-      <c r="H46" s="222"/>
+      <c r="D46" s="224"/>
+      <c r="E46" s="224"/>
+      <c r="F46" s="224"/>
+      <c r="G46" s="224"/>
+      <c r="H46" s="225"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C47" s="223"/>
-      <c r="D47" s="224"/>
-      <c r="E47" s="224"/>
-      <c r="F47" s="224"/>
-      <c r="G47" s="224"/>
-      <c r="H47" s="225"/>
+      <c r="C47" s="226"/>
+      <c r="D47" s="227"/>
+      <c r="E47" s="227"/>
+      <c r="F47" s="227"/>
+      <c r="G47" s="227"/>
+      <c r="H47" s="228"/>
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C48" s="226"/>
-      <c r="D48" s="227"/>
-      <c r="E48" s="227"/>
-      <c r="F48" s="227"/>
-      <c r="G48" s="227"/>
-      <c r="H48" s="228"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="230"/>
+      <c r="E48" s="230"/>
+      <c r="F48" s="230"/>
+      <c r="G48" s="230"/>
+      <c r="H48" s="231"/>
     </row>
     <row r="50" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="51" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C51" s="230" t="s">
+      <c r="C51" s="181" t="s">
         <v>156</v>
       </c>
-      <c r="D51" s="231">
+      <c r="D51" s="182">
         <f>D43+1</f>
         <v>7</v>
       </c>
@@ -7067,44 +7079,44 @@
       <c r="H51" s="149"/>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C52" s="232" t="s">
+      <c r="C52" s="183" t="s">
         <v>157</v>
       </c>
-      <c r="D52" s="233" t="s">
+      <c r="D52" s="184" t="s">
         <v>199</v>
       </c>
       <c r="H52" s="150"/>
     </row>
     <row r="53" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="232"/>
-      <c r="D53" s="233"/>
+      <c r="C53" s="183"/>
+      <c r="D53" s="184"/>
       <c r="H53" s="150"/>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C54" s="220" t="s">
+      <c r="C54" s="223" t="s">
         <v>202</v>
       </c>
-      <c r="D54" s="221"/>
-      <c r="E54" s="221"/>
-      <c r="F54" s="221"/>
-      <c r="G54" s="221"/>
-      <c r="H54" s="222"/>
+      <c r="D54" s="224"/>
+      <c r="E54" s="224"/>
+      <c r="F54" s="224"/>
+      <c r="G54" s="224"/>
+      <c r="H54" s="225"/>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C55" s="223"/>
-      <c r="D55" s="224"/>
-      <c r="E55" s="224"/>
-      <c r="F55" s="224"/>
-      <c r="G55" s="224"/>
-      <c r="H55" s="225"/>
+      <c r="C55" s="226"/>
+      <c r="D55" s="227"/>
+      <c r="E55" s="227"/>
+      <c r="F55" s="227"/>
+      <c r="G55" s="227"/>
+      <c r="H55" s="228"/>
     </row>
     <row r="56" spans="3:8" ht="67.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C56" s="226"/>
-      <c r="D56" s="227"/>
-      <c r="E56" s="227"/>
-      <c r="F56" s="227"/>
-      <c r="G56" s="227"/>
-      <c r="H56" s="228"/>
+      <c r="C56" s="229"/>
+      <c r="D56" s="230"/>
+      <c r="E56" s="230"/>
+      <c r="F56" s="230"/>
+      <c r="G56" s="230"/>
+      <c r="H56" s="231"/>
     </row>
   </sheetData>
   <mergeCells count="8">
